--- a/output/yearly_surface_area_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_5_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497623848861</v>
+        <v>10.84497621692697</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907161532182</v>
+        <v>37.78907154019078</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.048547605864599</v>
+        <v>5.540984042768997</v>
       </c>
       <c r="C2" t="n">
-        <v>3.534291735288517</v>
+        <v>6.207590733952582</v>
       </c>
       <c r="D2" t="n">
-        <v>25.10132530218245</v>
+        <v>18.11913562957913</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.6854241284803</v>
+        <v>18.68756755033803</v>
       </c>
       <c r="C3" t="n">
-        <v>22.74218556887736</v>
+        <v>33.61504139341078</v>
       </c>
       <c r="D3" t="n">
-        <v>57.21625620350412</v>
+        <v>67.26444395647022</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.87823189360694</v>
+        <v>38.61999118966102</v>
       </c>
       <c r="C4" t="n">
-        <v>56.02834148136547</v>
+        <v>87.88409098876598</v>
       </c>
       <c r="D4" t="n">
-        <v>75.49148971805847</v>
+        <v>93.35929793535043</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.84194828627883</v>
+        <v>43.31961744989052</v>
       </c>
       <c r="C5" t="n">
-        <v>65.5316592584746</v>
+        <v>126.8172596960817</v>
       </c>
       <c r="D5" t="n">
-        <v>63.76451339083034</v>
+        <v>69.80226177194822</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.9082651618111</v>
+        <v>39.24536447726626</v>
       </c>
       <c r="C6" t="n">
-        <v>71.00392096194632</v>
+        <v>132.5487027934746</v>
       </c>
       <c r="D6" t="n">
-        <v>46.85292743747478</v>
+        <v>47.45670227558657</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.32069700858599</v>
+        <v>28.26647990067416</v>
       </c>
       <c r="C7" t="n">
-        <v>77.31361345714056</v>
+        <v>106.4783925072006</v>
       </c>
       <c r="D7" t="n">
-        <v>40.54323494228053</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17.02350519163969</v>
+        <v>14.68694565553228</v>
       </c>
       <c r="C8" t="n">
-        <v>61.2512392679585</v>
+        <v>63.33745313948297</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -878,10 +878,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.209374302911826</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>39.93749660876023</v>
+        <v>36.60937189136354</v>
       </c>
       <c r="D9" t="n">
         <v>34.27968458918587</v>
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.694136684631501</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.98864530037232</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.721456416976546</v>
+        <v>7.684623284368366</v>
       </c>
       <c r="C21" t="n">
-        <v>95.55302316008475</v>
+        <v>94.13663523351248</v>
       </c>
       <c r="D21" t="n">
-        <v>8.686638469098613</v>
+        <v>8.645201194914412</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.962955629145879</v>
+        <v>6.937029278207961</v>
       </c>
       <c r="C2" t="n">
-        <v>10.79824299901067</v>
+        <v>7.384706231344508</v>
       </c>
       <c r="D2" t="n">
-        <v>33.50606739823939</v>
+        <v>19.39246240198725</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.5136182802371</v>
+        <v>18.47649179392497</v>
       </c>
       <c r="C3" t="n">
-        <v>17.74999849278233</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="D3" t="n">
-        <v>63.11165116750621</v>
+        <v>65.91454086313085</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.46607778427253</v>
+        <v>36.70558316637975</v>
       </c>
       <c r="C4" t="n">
-        <v>56.43674852633215</v>
+        <v>84.97419079337843</v>
       </c>
       <c r="D4" t="n">
-        <v>85.85481848408782</v>
+        <v>103.8247284626214</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.5304154688631</v>
+        <v>50.11822030179968</v>
       </c>
       <c r="C5" t="n">
-        <v>84.184865639164</v>
+        <v>143.6051454387022</v>
       </c>
       <c r="D5" t="n">
-        <v>74.49010705972675</v>
+        <v>83.84125394267762</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.09822549481625</v>
+        <v>47.77871552257953</v>
       </c>
       <c r="C6" t="n">
-        <v>87.74860980557993</v>
+        <v>163.2607162254276</v>
       </c>
       <c r="D6" t="n">
-        <v>55.62778841803278</v>
+        <v>57.07684802950107</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.20198765183014</v>
+        <v>36.65060529494193</v>
       </c>
       <c r="C7" t="n">
-        <v>89.82991493858314</v>
+        <v>146.4227613498905</v>
       </c>
       <c r="D7" t="n">
-        <v>44.25620475974196</v>
+        <v>43.29801900039708</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.61870634232051</v>
+        <v>21.86352137357647</v>
       </c>
       <c r="C8" t="n">
-        <v>82.6140693123691</v>
+        <v>98.46929473595507</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>12.53593643552752</v>
+        <v>10.98281156740907</v>
       </c>
       <c r="C9" t="n">
-        <v>58.13124506386212</v>
+        <v>56.13437023342411</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28954312395736</v>
+        <v>36.15776794741003</v>
       </c>
       <c r="D10" t="n">
-        <v>36.44247478164161</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.42774856607789</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
         <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.915083002616323</v>
+        <v>7.862501835470225</v>
       </c>
       <c r="C21" t="n">
-        <v>104.8748497846663</v>
+        <v>102.2125238611129</v>
       </c>
       <c r="D21" t="n">
-        <v>9.893853753270404</v>
+        <v>9.828127294337781</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.56989669454866</v>
+        <v>7.355253800217104</v>
       </c>
       <c r="C2" t="n">
-        <v>8.770933989741005</v>
+        <v>8.475427930762713</v>
       </c>
       <c r="D2" t="n">
-        <v>45.30569305558181</v>
+        <v>23.75927619047706</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.37050409959532</v>
+        <v>20.17982406079319</v>
       </c>
       <c r="C3" t="n">
-        <v>29.85494768614551</v>
+        <v>28.40196108386023</v>
       </c>
       <c r="D3" t="n">
-        <v>73.07148162709011</v>
+        <v>65.41875827248622</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.17704304859647</v>
+        <v>35.14853130744431</v>
       </c>
       <c r="C4" t="n">
-        <v>50.41274461307372</v>
+        <v>77.82706750646165</v>
       </c>
       <c r="D4" t="n">
-        <v>96.00118100747861</v>
+        <v>109.3892744502923</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.44482349214438</v>
+        <v>51.73810401380692</v>
       </c>
       <c r="C5" t="n">
-        <v>92.60335220308041</v>
+        <v>148.9802141194535</v>
       </c>
       <c r="D5" t="n">
-        <v>85.41205026947252</v>
+        <v>97.95387719122553</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.60390767796137</v>
+        <v>55.70829172978102</v>
       </c>
       <c r="C6" t="n">
-        <v>109.1222390747373</v>
+        <v>189.3437892318569</v>
       </c>
       <c r="D6" t="n">
-        <v>65.0869275484508</v>
+        <v>66.5762388157932</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.22112388429633</v>
+        <v>44.97484407925062</v>
       </c>
       <c r="C7" t="n">
-        <v>106.4185058972415</v>
+        <v>183.672232744423</v>
       </c>
       <c r="D7" t="n">
-        <v>48.98724694650735</v>
+        <v>48.50815406683489</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.13045893814036</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="C8" t="n">
-        <v>100.4720600526186</v>
+        <v>139.7763293921396</v>
       </c>
       <c r="D8" t="n">
-        <v>41.97462309507237</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.41562343626167</v>
+        <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>78.21093085882212</v>
+        <v>83.31405542549703</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.252972112526189</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>53.09782458418874</v>
+        <v>49.11192890494669</v>
       </c>
       <c r="D10" t="n">
-        <v>37.29659528433633</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.863979037466197</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>38.73780091417063</v>
+        <v>36.07235589714055</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>36.01639627799849</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.382120841130262</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>31.47974013667398</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>34.34153469455343</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>22.7323680918349</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>20.30548776693678</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>19.26188995732242</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.093699371656149</v>
+        <v>8.024404460123588</v>
       </c>
       <c r="C21" t="n">
-        <v>113.3117912031861</v>
+        <v>110.3355613266993</v>
       </c>
       <c r="D21" t="n">
-        <v>11.1288366360272</v>
+        <v>11.03355613266993</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10.18366893615216</v>
+        <v>6.7868218794582</v>
       </c>
       <c r="C2" t="n">
-        <v>5.753041546886309</v>
+        <v>5.830599615521806</v>
       </c>
       <c r="D2" t="n">
-        <v>36.30208485993431</v>
+        <v>19.63495408493621</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.49522711576367</v>
+        <v>24.23935081785375</v>
       </c>
       <c r="C3" t="n">
-        <v>42.42131830050468</v>
+        <v>44.36517875491336</v>
       </c>
       <c r="D3" t="n">
-        <v>80.8420147062036</v>
+        <v>72.58551651348793</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.55020498720149</v>
+        <v>24.84901614219102</v>
       </c>
       <c r="C4" t="n">
-        <v>75.26176075526473</v>
+        <v>116.957567502331</v>
       </c>
       <c r="D4" t="n">
-        <v>93.85704402140357</v>
+        <v>106.6070014564569</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.3982961349505</v>
+        <v>31.3668391506856</v>
       </c>
       <c r="C5" t="n">
-        <v>65.18804756198823</v>
+        <v>113.1218792218388</v>
       </c>
       <c r="D5" t="n">
-        <v>62.66004722355269</v>
+        <v>66.09616418841652</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.40258297866598</v>
+        <v>27.89439752076462</v>
       </c>
       <c r="C6" t="n">
-        <v>70.07813287684159</v>
+        <v>120.9562259017283</v>
       </c>
       <c r="D6" t="n">
-        <v>32.24157635516951</v>
+        <v>31.91956310817655</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>70.60631314172635</v>
+        <v>98.27392694280996</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46421209985527</v>
+        <v>28.26647990067416</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.76762889372977</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>57.57950285407543</v>
+        <v>61.33468782281948</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.656249434793372</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>27.5124976638126</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>28.18597658892593</v>
       </c>
       <c r="D10" t="n">
         <v>28.61303684027329</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.18753917370691</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.78680618392497</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.603594911662541</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>27.98864530037232</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.914048170382785</v>
+        <v>4.245077073163208</v>
       </c>
       <c r="C2" t="n">
-        <v>2.318888077430966</v>
+        <v>2.76067454434203</v>
       </c>
       <c r="D2" t="n">
-        <v>25.37425116396306</v>
+        <v>14.23828695469149</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>32.64311116620645</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="C3" t="n">
-        <v>32.37803928605981</v>
+        <v>34.03719290623692</v>
       </c>
       <c r="D3" t="n">
-        <v>91.32708018755955</v>
+        <v>71.88356690495145</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.47058561216627</v>
+        <v>34.12751369502762</v>
       </c>
       <c r="C4" t="n">
-        <v>93.72941681985148</v>
+        <v>117.1490083046591</v>
       </c>
       <c r="D4" t="n">
-        <v>109.7721560549486</v>
+        <v>118.0168732752133</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.20885988575987</v>
+        <v>35.39200473809752</v>
       </c>
       <c r="C5" t="n">
-        <v>101.3163630782709</v>
+        <v>162.3319828972101</v>
       </c>
       <c r="D5" t="n">
-        <v>77.77896186895356</v>
+        <v>82.68770039018762</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.60762938013333</v>
+        <v>33.24786775202249</v>
       </c>
       <c r="C6" t="n">
-        <v>87.0643316557199</v>
+        <v>150.6216962809542</v>
       </c>
       <c r="D6" t="n">
-        <v>40.53341746523807</v>
+        <v>39.80888765950392</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.43940636534185</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>86.6559246107532</v>
+        <v>127.498592602829</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>73.68507394224434</v>
+        <v>83.28165775125692</v>
       </c>
       <c r="D8" t="n">
-        <v>28.62285431731576</v>
+        <v>28.37250865273282</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>47.03749600587317</v>
+        <v>42.15624642035802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.2776546738526</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.69109363052753</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.67163860289184</v>
+        <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.69185439405351</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.194828013797373</v>
+        <v>4.34619708670063</v>
       </c>
       <c r="C2" t="n">
-        <v>6.831982273853553</v>
+        <v>7.774460069930491</v>
       </c>
       <c r="D2" t="n">
-        <v>22.10012257029995</v>
+        <v>23.10641396715293</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.49737053762141</v>
+        <v>19.6055016538088</v>
       </c>
       <c r="C3" t="n">
-        <v>19.30606860401353</v>
+        <v>21.75062038758809</v>
       </c>
       <c r="D3" t="n">
-        <v>90.15880041950584</v>
+        <v>66.95519342963247</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.4337622254904</v>
+        <v>39.97283952611313</v>
       </c>
       <c r="C4" t="n">
-        <v>87.71817562674826</v>
+        <v>100.6723365842849</v>
       </c>
       <c r="D4" t="n">
-        <v>128.4950665226395</v>
+        <v>125.6617426481832</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.78090000216628</v>
+        <v>42.73056882734243</v>
       </c>
       <c r="C5" t="n">
-        <v>137.8373776762522</v>
+        <v>190.1154429273949</v>
       </c>
       <c r="D5" t="n">
-        <v>97.16847902782808</v>
+        <v>102.3226544751238</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.85921883432777</v>
+        <v>40.17115256237099</v>
       </c>
       <c r="C6" t="n">
-        <v>124.2166100275319</v>
+        <v>200.2117363178691</v>
       </c>
       <c r="D6" t="n">
-        <v>53.33344403320799</v>
+        <v>53.05168244208915</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.15910954801276</v>
+        <v>26.70942804173872</v>
       </c>
       <c r="C7" t="n">
-        <v>106.7778255569958</v>
+        <v>170.3175187235536</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.85522542358599</v>
+        <v>13.10142311317368</v>
       </c>
       <c r="C8" t="n">
-        <v>94.12996988318417</v>
+        <v>121.9183386518901</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>67.33905678199295</v>
+        <v>68.00468172547228</v>
       </c>
       <c r="D9" t="n">
-        <v>30.50780990946962</v>
+        <v>29.50937249425062</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
         <v>30.32127784566274</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.954659679155399</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.74146586308036</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
-        <v>29.72437524148068</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.29272504678157</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.53664044579129</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
         <v>10.86107485208246</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.59810533606456</v>
+        <v>2.581996462169111</v>
       </c>
       <c r="C2" t="n">
-        <v>3.020837685967436</v>
+        <v>3.6471927212769</v>
       </c>
       <c r="D2" t="n">
-        <v>15.29955622298229</v>
+        <v>16.14091400552181</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.64463269325843</v>
+        <v>19.57114048416017</v>
       </c>
       <c r="C3" t="n">
-        <v>23.96937019918587</v>
+        <v>26.84098223410779</v>
       </c>
       <c r="D3" t="n">
-        <v>90.27170140549421</v>
+        <v>70.50421138048469</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>57.59815606045612</v>
+        <v>43.80165557267569</v>
       </c>
       <c r="C4" t="n">
-        <v>81.82179891504191</v>
+        <v>93.83151858109315</v>
       </c>
       <c r="D4" t="n">
-        <v>140.9131932336574</v>
+        <v>132.5663742521511</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.01437602932777</v>
+        <v>44.25227776892498</v>
       </c>
       <c r="C5" t="n">
-        <v>162.8228567493335</v>
+        <v>221.4331946928681</v>
       </c>
       <c r="D5" t="n">
-        <v>105.955120980837</v>
+        <v>107.673179463269</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.29190752999335</v>
+        <v>32.88560284915541</v>
       </c>
       <c r="C6" t="n">
-        <v>156.5386896944497</v>
+        <v>236.3979749487023</v>
       </c>
       <c r="D6" t="n">
-        <v>52.68941753922207</v>
+        <v>51.92463607761381</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.4801567428347</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>117.5574153496258</v>
+        <v>170.9762714331032</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>34.61446055633404</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>80.02716411167874</v>
+        <v>87.12029127486194</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
         <v>9.092947236733956</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.105088062083413</v>
+        <v>3.437098712568083</v>
       </c>
       <c r="C2" t="n">
-        <v>3.380157345721768</v>
+        <v>5.089380098815464</v>
       </c>
       <c r="D2" t="n">
-        <v>16.77905001328224</v>
+        <v>17.8668264695877</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.58095796120263</v>
+        <v>14.40223882130071</v>
       </c>
       <c r="C3" t="n">
-        <v>17.3278469799562</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D3" t="n">
-        <v>82.94295479329178</v>
+        <v>67.82894888641214</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>54.62444226429253</v>
+        <v>41.15977250054753</v>
       </c>
       <c r="C4" t="n">
-        <v>71.1649275854428</v>
+        <v>81.46444275069608</v>
       </c>
       <c r="D4" t="n">
-        <v>151.9274207276024</v>
+        <v>136.3186139777824</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.6732519120644</v>
+        <v>53.30890034060182</v>
       </c>
       <c r="C5" t="n">
-        <v>158.4049920802229</v>
+        <v>198.7057353395545</v>
       </c>
       <c r="D5" t="n">
-        <v>128.0689880189964</v>
+        <v>125.5900750657732</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.93092747446678</v>
+        <v>42.94851681768522</v>
       </c>
       <c r="C6" t="n">
-        <v>205.3236966138822</v>
+        <v>292.3880282696021</v>
       </c>
       <c r="D6" t="n">
-        <v>69.39385472698156</v>
+        <v>67.98504677138737</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.47555110394973</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>168.4011472048639</v>
+        <v>243.3791828736013</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>40.00425545264903</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.926230053461247</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>113.5734831657923</v>
+        <v>144.3659999094935</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.773437264497239</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>59.24061996966101</v>
+        <v>57.68749510154256</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>25.41057582902019</v>
+        <v>23.98900515327081</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.82791641431633</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.44249047717483</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.57356164345839</v>
+        <v>2.317906329726719</v>
       </c>
       <c r="C2" t="n">
-        <v>2.105848825609408</v>
+        <v>3.655046702910875</v>
       </c>
       <c r="D2" t="n">
-        <v>12.99932135193201</v>
+        <v>12.80788054960389</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.8986433067511</v>
+        <v>13.40085616296896</v>
       </c>
       <c r="C3" t="n">
-        <v>15.66869335977909</v>
+        <v>20.33199495495144</v>
       </c>
       <c r="D3" t="n">
-        <v>79.2123135171539</v>
+        <v>67.36752746541613</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.23857435879452</v>
+        <v>36.92254940901829</v>
       </c>
       <c r="C4" t="n">
-        <v>60.01031016979053</v>
+        <v>70.67994421954486</v>
       </c>
       <c r="D4" t="n">
-        <v>157.3260513532556</v>
+        <v>138.4755136840126</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>75.39822368615505</v>
+        <v>58.16855147662353</v>
       </c>
       <c r="C5" t="n">
-        <v>152.9072049364407</v>
+        <v>187.2683745850791</v>
       </c>
       <c r="D5" t="n">
-        <v>144.292368831675</v>
+        <v>137.3955912093411</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>64.40264939859078</v>
+        <v>50.27431818677493</v>
       </c>
       <c r="C6" t="n">
-        <v>231.6482795555562</v>
+        <v>314.7276972797383</v>
       </c>
       <c r="D6" t="n">
-        <v>84.08570912103508</v>
+        <v>81.06683493047613</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.93657161431823</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="C7" t="n">
-        <v>216.130775342231</v>
+        <v>302.6070401231071</v>
       </c>
       <c r="D7" t="n">
-        <v>46.53189593818607</v>
+        <v>44.43586458961913</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>4.506221962492859</v>
       </c>
       <c r="C8" t="n">
-        <v>146.201868116435</v>
+        <v>191.0971906316416</v>
       </c>
       <c r="D8" t="n">
-        <v>36.38356991938679</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>71.66561891460864</v>
+        <v>66.34061936677394</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>34.16482010778901</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.96750451476862</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.792712365683681</v>
+        <v>3.737513510067607</v>
       </c>
       <c r="C2" t="n">
-        <v>9.256899103343175</v>
+        <v>14.5887708851076</v>
       </c>
       <c r="D2" t="n">
-        <v>12.82260676516759</v>
+        <v>12.43972516051134</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.55579237379071</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="C3" t="n">
-        <v>12.080405500757</v>
+        <v>17.36220814960484</v>
       </c>
       <c r="D3" t="n">
-        <v>72.19281743178919</v>
+        <v>62.65513848503144</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.17628228507048</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="C4" t="n">
-        <v>50.24682925105601</v>
+        <v>61.68222651012285</v>
       </c>
       <c r="D4" t="n">
-        <v>160.0062225858494</v>
+        <v>139.5475821770501</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>74.90734983403165</v>
+        <v>57.0395416167397</v>
       </c>
       <c r="C5" t="n">
-        <v>133.8612994740526</v>
+        <v>162.6510509010903</v>
       </c>
       <c r="D5" t="n">
-        <v>162.6755945936965</v>
+        <v>150.5264667536422</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>79.33601372788901</v>
+        <v>60.73974871404592</v>
       </c>
       <c r="C6" t="n">
-        <v>237.2835113779329</v>
+        <v>309.1327171132357</v>
       </c>
       <c r="D6" t="n">
-        <v>103.4870072523605</v>
+        <v>98.01278205348032</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>41.98051358129786</v>
+        <v>30.9014907388726</v>
       </c>
       <c r="C7" t="n">
-        <v>266.3756410978785</v>
+        <v>367.1049190490098</v>
       </c>
       <c r="D7" t="n">
-        <v>56.05386692167588</v>
+        <v>52.939763203805</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.93314334511998</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>205.283444958008</v>
+        <v>270.0395235301276</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3.106249736236907</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>114.3765527878661</v>
+        <v>127.578114166873</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>52.52841091572559</v>
+        <v>47.68839473378882</v>
       </c>
       <c r="D10" t="n">
-        <v>27.75891633757857</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.29148125717007</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.049529353568845</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C2" t="n">
-        <v>6.046584110456105</v>
+        <v>5.133558745506572</v>
       </c>
       <c r="D2" t="n">
-        <v>12.93059901263474</v>
+        <v>11.59247689174634</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.750677140850315</v>
+        <v>2.702751429791469</v>
       </c>
       <c r="C2" t="n">
-        <v>5.109996800604648</v>
+        <v>8.40277860064845</v>
       </c>
       <c r="D2" t="n">
-        <v>9.436558933220342</v>
+        <v>9.254935607934682</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.87824758914017</v>
+        <v>14.5740446695439</v>
       </c>
       <c r="C3" t="n">
-        <v>21.56408832378119</v>
+        <v>31.33738671955819</v>
       </c>
       <c r="D3" t="n">
-        <v>76.949385058865</v>
+        <v>67.23499152534281</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>58.08313942635404</v>
+        <v>43.46982484864026</v>
       </c>
       <c r="C4" t="n">
-        <v>72.19870791801469</v>
+        <v>90.33453325856601</v>
       </c>
       <c r="D4" t="n">
-        <v>163.8733267928776</v>
+        <v>143.3636355034575</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.46750150033328</v>
+        <v>35.26928627506667</v>
       </c>
       <c r="C5" t="n">
-        <v>200.5465122850172</v>
+        <v>254.2235680147116</v>
       </c>
       <c r="D5" t="n">
-        <v>149.5938064346078</v>
+        <v>137.6410281354028</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.04282135055514</v>
+        <v>19.15978819608075</v>
       </c>
       <c r="C6" t="n">
-        <v>226.6168225712913</v>
+        <v>299.3515647358248</v>
       </c>
       <c r="D6" t="n">
-        <v>82.43539123019619</v>
+        <v>78.32972233103602</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.905032514595317</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>144.3267300013236</v>
+        <v>189.9004401801648</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.086213871524472</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>84.28304040958866</v>
+        <v>94.04652132832319</v>
       </c>
       <c r="D8" t="n">
-        <v>25.20146356801562</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>40.04843409934012</v>
+        <v>36.38749691020377</v>
       </c>
       <c r="D9" t="n">
-        <v>21.1890607007589</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>23.77302065833652</v>
+        <v>21.92242623583128</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="D11" t="n">
-        <v>16.8811517745239</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>10.14636252339079</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.864379948093698</v>
+        <v>6.706318567709961</v>
       </c>
       <c r="C2" t="n">
-        <v>4.237223091529233</v>
+        <v>5.103124566674921</v>
       </c>
       <c r="D2" t="n">
-        <v>14.93827306781947</v>
+        <v>14.25988540418492</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.85107744859075</v>
+        <v>11.54535300194249</v>
       </c>
       <c r="C3" t="n">
-        <v>15.2367243699105</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="D3" t="n">
-        <v>13.99972226255952</v>
+        <v>12.87562114119692</v>
       </c>
     </row>
     <row r="4">
@@ -4554,7 +4554,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
         <v>9.35114688295087</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39770562934005</v>
+        <v>13.39819766108588</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14092947125087</v>
+        <v>70.14350540215547</v>
       </c>
       <c r="D21" t="n">
-        <v>1.5762006622753</v>
+        <v>1.576258548363044</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.459098072689013</v>
+        <v>4.413937678293659</v>
       </c>
       <c r="C2" t="n">
-        <v>2.734167356327367</v>
+        <v>9.231373663032759</v>
       </c>
       <c r="D2" t="n">
-        <v>16.929257412032</v>
+        <v>24.87846857331843</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.36497346626834</v>
+        <v>18.49612674800991</v>
       </c>
       <c r="C3" t="n">
-        <v>16.04175748739288</v>
+        <v>17.49474408967816</v>
       </c>
       <c r="D3" t="n">
-        <v>23.16433708170349</v>
+        <v>21.74080291054562</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.94514530174919</v>
+        <v>13.464669763745</v>
       </c>
       <c r="C4" t="n">
-        <v>23.76418492899829</v>
+        <v>20.25443688631594</v>
       </c>
       <c r="D4" t="n">
-        <v>22.41133659254619</v>
+        <v>21.81148874525138</v>
       </c>
     </row>
     <row r="5">
@@ -4865,7 +4865,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
         <v>5.424156065963628</v>
@@ -4885,7 +4885,7 @@
         <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4409446111677</v>
+        <v>15.44236840005066</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14421730440925</v>
+        <v>86.15216054765105</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250725181298463</v>
+        <v>3.251024926326455</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.504258467084366</v>
+        <v>4.487568756112171</v>
       </c>
       <c r="C2" t="n">
-        <v>2.651700549170635</v>
+        <v>6.484443586550183</v>
       </c>
       <c r="D2" t="n">
-        <v>20.02372617581795</v>
+        <v>23.14372037991431</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.15113239319178</v>
+        <v>16.68480223367454</v>
       </c>
       <c r="C3" t="n">
-        <v>12.76272015520853</v>
+        <v>28.6719417025281</v>
       </c>
       <c r="D3" t="n">
-        <v>31.33247798103696</v>
+        <v>36.59955441432109</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.63128913602648</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="C4" t="n">
-        <v>33.42556408649115</v>
+        <v>34.11475097487241</v>
       </c>
       <c r="D4" t="n">
-        <v>28.98413747247858</v>
+        <v>27.8099672181994</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.27813769993811</v>
+        <v>12.10004045484194</v>
       </c>
       <c r="C5" t="n">
-        <v>27.29258617806133</v>
+        <v>23.63557597974196</v>
       </c>
       <c r="D5" t="n">
-        <v>30.48326621686347</v>
+        <v>30.26237298340794</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5249,7 +5249,7 @@
         <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73670734036052</v>
+        <v>16.73660015442623</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0939147761992</v>
+        <v>102.093260942</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021012202108158</v>
+        <v>5.02098004632787</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.505641125416113</v>
+        <v>5.253331965424683</v>
       </c>
       <c r="C2" t="n">
-        <v>3.517602024316322</v>
+        <v>8.985936736971055</v>
       </c>
       <c r="D2" t="n">
-        <v>15.60684325441155</v>
+        <v>23.74062298409637</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.20865459711484</v>
+        <v>15.96812640957437</v>
       </c>
       <c r="C3" t="n">
-        <v>11.30973355292326</v>
+        <v>26.63481521621597</v>
       </c>
       <c r="D3" t="n">
-        <v>39.57915869671016</v>
+        <v>46.04887606769665</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.56671477172444</v>
+        <v>29.57122259961817</v>
       </c>
       <c r="C4" t="n">
-        <v>32.5959872764026</v>
+        <v>54.80312034646545</v>
       </c>
       <c r="D4" t="n">
-        <v>37.39477005476101</v>
+        <v>39.24536447726624</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.68528525976006</v>
+        <v>25.45180923259857</v>
       </c>
       <c r="C5" t="n">
-        <v>46.24031687002478</v>
+        <v>45.28311285838414</v>
       </c>
       <c r="D5" t="n">
-        <v>34.14027641518284</v>
+        <v>33.06035394051135</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.95474179461341</v>
+        <v>11.23021198887927</v>
       </c>
       <c r="C6" t="n">
-        <v>28.49817235887642</v>
+        <v>25.51954982419159</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>38.35982804803563</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
         <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.54355373745002</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
         <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5574,10 +5574,10 @@
         <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>46.86470840992573</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>46.30903920932205</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06799302268903</v>
+        <v>18.06383823521628</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8721449575427</v>
+        <v>117.8450399154586</v>
       </c>
       <c r="D21" t="n">
-        <v>6.883044961024391</v>
+        <v>6.881462184844297</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.512734343524093</v>
+        <v>6.976299186377835</v>
       </c>
       <c r="C2" t="n">
-        <v>6.603235058764047</v>
+        <v>10.53807985738526</v>
       </c>
       <c r="D2" t="n">
-        <v>20.09441201052372</v>
+        <v>30.89363675723863</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.86013416210722</v>
+        <v>15.22690689286803</v>
       </c>
       <c r="C3" t="n">
-        <v>11.93314334511998</v>
+        <v>29.47697482001048</v>
       </c>
       <c r="D3" t="n">
-        <v>40.11421119552467</v>
+        <v>50.66309027765665</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.55172651425348</v>
+        <v>21.92635322664826</v>
       </c>
       <c r="C4" t="n">
-        <v>25.25742318715769</v>
+        <v>50.99982974021331</v>
       </c>
       <c r="D4" t="n">
-        <v>41.73409490753191</v>
+        <v>46.00960615952677</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.92380889416302</v>
+        <v>21.57390580082366</v>
       </c>
       <c r="C5" t="n">
-        <v>39.76078202199582</v>
+        <v>56.40140560897927</v>
       </c>
       <c r="D5" t="n">
-        <v>32.42221793275092</v>
+        <v>31.63681976935347</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.6050596854523</v>
+        <v>12.39751000922872</v>
       </c>
       <c r="C6" t="n">
-        <v>35.58246379272141</v>
+        <v>33.73088762251191</v>
       </c>
       <c r="D6" t="n">
-        <v>31.31578827006476</v>
+        <v>31.23528495831652</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>20.18178755620168</v>
+        <v>18.68462230722529</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.77592484372025</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.2984356065578</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.47308888692249</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065806332494906</v>
+        <v>7.060454745546799</v>
       </c>
       <c r="C21" t="n">
-        <v>66.24193436713973</v>
+        <v>66.19176323950123</v>
       </c>
       <c r="D21" t="n">
-        <v>5.299354749371179</v>
+        <v>5.295341059160099</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.721044783273664</v>
+        <v>6.472662614099221</v>
       </c>
       <c r="C2" t="n">
-        <v>7.493680226515903</v>
+        <v>9.64665294192916</v>
       </c>
       <c r="D2" t="n">
-        <v>17.15604113171301</v>
+        <v>22.95129782988193</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.60259746842507</v>
+        <v>20.88668240785089</v>
       </c>
       <c r="C3" t="n">
-        <v>21.1762979806037</v>
+        <v>37.02170592714722</v>
       </c>
       <c r="D3" t="n">
-        <v>47.71784716491622</v>
+        <v>64.37319696746336</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.00140802052752</v>
+        <v>27.01867856857647</v>
       </c>
       <c r="C4" t="n">
-        <v>28.32047602440774</v>
+        <v>65.43446623575416</v>
       </c>
       <c r="D4" t="n">
-        <v>53.66723825265188</v>
+        <v>61.43973482717389</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.94330497952772</v>
+        <v>28.47068342315751</v>
       </c>
       <c r="C5" t="n">
-        <v>44.25227776892498</v>
+        <v>79.61973881441634</v>
       </c>
       <c r="D5" t="n">
-        <v>40.76707341884881</v>
+        <v>42.11697651218817</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.11074186859742</v>
+        <v>21.93715245139498</v>
       </c>
       <c r="C6" t="n">
-        <v>52.44790760397736</v>
+        <v>66.25422556880025</v>
       </c>
       <c r="D6" t="n">
-        <v>35.26045054572845</v>
+        <v>34.73717901936489</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.91743538185203</v>
+        <v>10.89936301254809</v>
       </c>
       <c r="C7" t="n">
-        <v>39.1059563032632</v>
+        <v>36.53083207502382</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.9248473951295</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>23.94973524510094</v>
+        <v>22.61455836732527</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.62968549351647</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6179,7 +6179,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
         <v>24.76949457814703</v>
@@ -6199,7 +6199,7 @@
         <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>32.97886888105885</v>
       </c>
     </row>
     <row r="13">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6305,7 +6305,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>10.75995483854504</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.295205560359568</v>
+        <v>7.282430528482158</v>
       </c>
       <c r="C21" t="n">
-        <v>76.59965838377546</v>
+        <v>75.5552167330024</v>
       </c>
       <c r="D21" t="n">
-        <v>6.383304865314622</v>
+        <v>6.372126712421888</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.240569245269474</v>
+        <v>4.718279466610171</v>
       </c>
       <c r="C2" t="n">
-        <v>5.230751768227005</v>
+        <v>7.930557954905733</v>
       </c>
       <c r="D2" t="n">
-        <v>23.51383926441536</v>
+        <v>19.30214161319654</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.97918767622835</v>
+        <v>21.76043786463055</v>
       </c>
       <c r="C3" t="n">
-        <v>26.21266370338984</v>
+        <v>37.3358651925062</v>
       </c>
       <c r="D3" t="n">
-        <v>50.59927667688061</v>
+        <v>67.79949645528473</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.96007680595792</v>
+        <v>34.86775146402972</v>
       </c>
       <c r="C4" t="n">
-        <v>43.38048580755381</v>
+        <v>81.52825635147212</v>
       </c>
       <c r="D4" t="n">
-        <v>66.22575488537709</v>
+        <v>79.90739089176064</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.86462629446773</v>
+        <v>34.9993056563988</v>
       </c>
       <c r="C5" t="n">
-        <v>48.67014243803564</v>
+        <v>103.2307711015521</v>
       </c>
       <c r="D5" t="n">
-        <v>51.49266708774522</v>
+        <v>54.29064804484862</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.77113927838603</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="C6" t="n">
-        <v>62.9938414429966</v>
+        <v>99.42159000907451</v>
       </c>
       <c r="D6" t="n">
-        <v>40.17115256237099</v>
+        <v>40.49316580936395</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.25974653546468</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>60.42558944868693</v>
+        <v>68.33062196328224</v>
       </c>
       <c r="D7" t="n">
-        <v>36.9500383447372</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>40.05530633326986</v>
+        <v>36.96770980341364</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>26.5140602485936</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.47420950334699</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.514579671674223</v>
+        <v>7.491076028076905</v>
       </c>
       <c r="C21" t="n">
-        <v>86.41766622425357</v>
+        <v>85.21098981937479</v>
       </c>
       <c r="D21" t="n">
-        <v>7.514579671674223</v>
+        <v>7.491076028076905</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_5_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497621692697</v>
+        <v>10.84497626192125</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907154019078</v>
+        <v>37.78907169697234</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.540984042768997</v>
+        <v>7.056802498126073</v>
       </c>
       <c r="C2" t="n">
-        <v>6.207590733952582</v>
+        <v>9.53866069446201</v>
       </c>
       <c r="D2" t="n">
-        <v>18.11913562957913</v>
+        <v>36.92353115672254</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.68756755033803</v>
+        <v>20.59215809657685</v>
       </c>
       <c r="C3" t="n">
-        <v>33.61504139341078</v>
+        <v>24.94130042639022</v>
       </c>
       <c r="D3" t="n">
-        <v>67.26444395647022</v>
+        <v>103.4663905505714</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.61999118966102</v>
+        <v>38.82419471214436</v>
       </c>
       <c r="C4" t="n">
-        <v>87.88409098876598</v>
+        <v>65.45999167606458</v>
       </c>
       <c r="D4" t="n">
-        <v>93.35929793535043</v>
+        <v>102.7016090889631</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.31961744989052</v>
+        <v>47.07480241863456</v>
       </c>
       <c r="C5" t="n">
-        <v>126.8172596960817</v>
+        <v>120.4849870036898</v>
       </c>
       <c r="D5" t="n">
-        <v>69.80226177194822</v>
+        <v>65.26167863980673</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.24536447726626</v>
+        <v>42.18373535607696</v>
       </c>
       <c r="C6" t="n">
-        <v>132.5487027934746</v>
+        <v>135.2455637370406</v>
       </c>
       <c r="D6" t="n">
-        <v>47.45670227558657</v>
+        <v>44.39757642915352</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.26647990067416</v>
+        <v>28.62579956042849</v>
       </c>
       <c r="C7" t="n">
-        <v>106.4783925072006</v>
+        <v>105.87952640761</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>38.08788393395925</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.68694565553228</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>63.33745313948297</v>
+        <v>64.83952712698058</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>36.04977569994287</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>36.60937189136354</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.684623284368366</v>
+        <v>7.680927238967817</v>
       </c>
       <c r="C21" t="n">
-        <v>94.13663523351248</v>
+        <v>94.09135867735574</v>
       </c>
       <c r="D21" t="n">
-        <v>8.645201194914412</v>
+        <v>8.641043143838793</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.937029278207961</v>
+        <v>8.598146393793566</v>
       </c>
       <c r="C2" t="n">
-        <v>7.384706231344508</v>
+        <v>5.781512230309467</v>
       </c>
       <c r="D2" t="n">
-        <v>19.39246240198725</v>
+        <v>30.21230385049135</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.47649179392497</v>
+        <v>22.0991408225957</v>
       </c>
       <c r="C3" t="n">
-        <v>28.62285431731576</v>
+        <v>30.90541772968959</v>
       </c>
       <c r="D3" t="n">
-        <v>65.91454086313085</v>
+        <v>107.5455522617168</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.70558316637975</v>
+        <v>38.41578766717769</v>
       </c>
       <c r="C4" t="n">
-        <v>84.97419079337843</v>
+        <v>63.80083805588747</v>
       </c>
       <c r="D4" t="n">
-        <v>103.8247284626214</v>
+        <v>126.7210484210655</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.11822030179968</v>
+        <v>51.76264770641309</v>
       </c>
       <c r="C5" t="n">
-        <v>143.6051454387022</v>
+        <v>119.2578023733813</v>
       </c>
       <c r="D5" t="n">
-        <v>83.84125394267762</v>
+        <v>82.95768100885549</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.77871552257953</v>
+        <v>51.64287448649497</v>
       </c>
       <c r="C6" t="n">
-        <v>163.2607162254276</v>
+        <v>161.4493917110922</v>
       </c>
       <c r="D6" t="n">
-        <v>57.07684802950107</v>
+        <v>53.41394734495622</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.65060529494193</v>
+        <v>38.62686342359076</v>
       </c>
       <c r="C7" t="n">
-        <v>146.4227613498905</v>
+        <v>145.883781860259</v>
       </c>
       <c r="D7" t="n">
-        <v>43.29801900039708</v>
+        <v>41.3816474817073</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.86352137357647</v>
+        <v>22.03041848329842</v>
       </c>
       <c r="C8" t="n">
-        <v>98.46929473595507</v>
+        <v>99.63757450400877</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>38.13598957146735</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.98281156740907</v>
+        <v>10.87187407682917</v>
       </c>
       <c r="C9" t="n">
-        <v>56.13437023342411</v>
+        <v>56.91093266748334</v>
       </c>
       <c r="D9" t="n">
-        <v>35.38905949498476</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>36.15776794741003</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.862501835470225</v>
+        <v>7.855765355942813</v>
       </c>
       <c r="C21" t="n">
-        <v>102.2125238611129</v>
+        <v>102.1249496272566</v>
       </c>
       <c r="D21" t="n">
-        <v>9.828127294337781</v>
+        <v>9.819706694928517</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.355253800217104</v>
+        <v>8.724791847641404</v>
       </c>
       <c r="C2" t="n">
-        <v>8.475427930762713</v>
+        <v>7.600690726278806</v>
       </c>
       <c r="D2" t="n">
-        <v>23.75927619047706</v>
+        <v>33.27044794922016</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.17982406079319</v>
+        <v>24.58296251434013</v>
       </c>
       <c r="C3" t="n">
-        <v>28.40196108386023</v>
+        <v>26.78698611037422</v>
       </c>
       <c r="D3" t="n">
-        <v>65.41875827248622</v>
+        <v>105.8814899030185</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.14853130744431</v>
+        <v>39.05392367493812</v>
       </c>
       <c r="C4" t="n">
-        <v>77.82706750646165</v>
+        <v>68.84211251719483</v>
       </c>
       <c r="D4" t="n">
-        <v>109.3892744502923</v>
+        <v>143.6571780670273</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.73810401380692</v>
+        <v>54.21701696703012</v>
       </c>
       <c r="C5" t="n">
-        <v>148.9802141194535</v>
+        <v>117.048870038826</v>
       </c>
       <c r="D5" t="n">
-        <v>97.95387719122553</v>
+        <v>103.5743827980385</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.70829172978102</v>
+        <v>58.6064109527176</v>
       </c>
       <c r="C6" t="n">
-        <v>189.3437892318569</v>
+        <v>173.7663984085727</v>
       </c>
       <c r="D6" t="n">
-        <v>66.5762388157932</v>
+        <v>63.27560303411543</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>44.97484407925062</v>
+        <v>47.66974152740813</v>
       </c>
       <c r="C7" t="n">
-        <v>183.672232744423</v>
+        <v>181.3366549560199</v>
       </c>
       <c r="D7" t="n">
-        <v>48.50815406683489</v>
+        <v>46.17257627843174</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.45733986592554</v>
+        <v>29.95803119509142</v>
       </c>
       <c r="C8" t="n">
-        <v>139.7763293921396</v>
+        <v>138.190806849781</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>39.80496066868692</v>
       </c>
     </row>
     <row r="9">
@@ -1503,10 +1503,10 @@
         <v>15.42031119060464</v>
       </c>
       <c r="C9" t="n">
-        <v>83.31405542549703</v>
+        <v>84.97811778419538</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.16405934426299</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>49.11192890494669</v>
+        <v>49.68134257340984</v>
       </c>
       <c r="D10" t="n">
-        <v>36.15776794741003</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.78314123501524</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.69925071179776</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,7 +1601,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1629,7 +1629,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.024404460123588</v>
+        <v>8.014681653236002</v>
       </c>
       <c r="C21" t="n">
-        <v>110.3355613266993</v>
+        <v>109.2000375253405</v>
       </c>
       <c r="D21" t="n">
-        <v>11.03355613266993</v>
+        <v>11.0201872731995</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.7868218794582</v>
+        <v>8.119053514121122</v>
       </c>
       <c r="C2" t="n">
-        <v>5.830599615521806</v>
+        <v>5.228788272818512</v>
       </c>
       <c r="D2" t="n">
-        <v>19.63495408493621</v>
+        <v>27.63227088373073</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.23935081785375</v>
+        <v>28.08289307998001</v>
       </c>
       <c r="C3" t="n">
-        <v>44.36517875491336</v>
+        <v>41.1548637620263</v>
       </c>
       <c r="D3" t="n">
-        <v>72.58551651348793</v>
+        <v>113.5342132576224</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.84901614219102</v>
+        <v>26.04871183678062</v>
       </c>
       <c r="C4" t="n">
-        <v>116.957567502331</v>
+        <v>95.43962132064942</v>
       </c>
       <c r="D4" t="n">
-        <v>106.6070014564569</v>
+        <v>130.9965596730604</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.3668391506856</v>
+        <v>33.011266555299</v>
       </c>
       <c r="C5" t="n">
-        <v>113.1218792218388</v>
+        <v>103.8198197241002</v>
       </c>
       <c r="D5" t="n">
-        <v>66.09616418841652</v>
+        <v>65.62983402889928</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.89439752076462</v>
+        <v>29.58496706747763</v>
       </c>
       <c r="C6" t="n">
-        <v>120.9562259017283</v>
+        <v>119.4266629785118</v>
       </c>
       <c r="D6" t="n">
-        <v>31.91956310817655</v>
+        <v>30.39000018496002</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="C7" t="n">
-        <v>98.27392694280996</v>
+        <v>97.13608135358791</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>27.96704685087888</v>
       </c>
     </row>
     <row r="8">
@@ -1800,10 +1800,10 @@
         <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>61.33468782281948</v>
+        <v>62.58641614573416</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.37112599440107</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>37.49687181600267</v>
+        <v>37.94062177832222</v>
       </c>
       <c r="D9" t="n">
-        <v>27.5124976638126</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,7 +1898,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>22.57528845915541</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
         <v>17.47216389248049</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.245077073163208</v>
+        <v>4.925428232206248</v>
       </c>
       <c r="C2" t="n">
-        <v>2.76067454434203</v>
+        <v>2.440624792757571</v>
       </c>
       <c r="D2" t="n">
-        <v>14.23828695469149</v>
+        <v>19.74294633240336</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.48478774391545</v>
+        <v>28.69648539513427</v>
       </c>
       <c r="C3" t="n">
-        <v>34.03719290623692</v>
+        <v>31.396291581813</v>
       </c>
       <c r="D3" t="n">
-        <v>71.88356690495145</v>
+        <v>111.4332731705342</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.12751369502762</v>
+        <v>37.39477005476101</v>
       </c>
       <c r="C4" t="n">
-        <v>117.1490083046591</v>
+        <v>101.412574353287</v>
       </c>
       <c r="D4" t="n">
-        <v>118.0168732752133</v>
+        <v>151.9146580074472</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.39200473809752</v>
+        <v>36.76645152404306</v>
       </c>
       <c r="C5" t="n">
-        <v>162.3319828972101</v>
+        <v>138.7700379952867</v>
       </c>
       <c r="D5" t="n">
-        <v>82.68770039018762</v>
+        <v>88.74999246391167</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.24786775202249</v>
+        <v>35.30070220160257</v>
       </c>
       <c r="C6" t="n">
-        <v>150.6216962809542</v>
+        <v>142.6116167620044</v>
       </c>
       <c r="D6" t="n">
-        <v>39.80888765950392</v>
+        <v>37.55479493055324</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>18.50496247734813</v>
       </c>
       <c r="C7" t="n">
-        <v>127.498592602829</v>
+        <v>126.9596131131975</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>30.3625112492411</v>
       </c>
     </row>
     <row r="8">
@@ -2111,10 +2111,10 @@
         <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>83.28165775125692</v>
+        <v>82.94786353181301</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>28.12216298814988</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
         <v>30.03657101143117</v>
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
         <v>28.42257778564941</v>
@@ -2184,7 +2184,7 @@
         <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2195,7 +2195,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
         <v>18.74450891718435</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.34619708670063</v>
+        <v>5.436918786118836</v>
       </c>
       <c r="C2" t="n">
-        <v>7.774460069930491</v>
+        <v>5.594980166502572</v>
       </c>
       <c r="D2" t="n">
-        <v>23.10641396715293</v>
+        <v>21.20575041173111</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.6055016538088</v>
+        <v>22.69800692218626</v>
       </c>
       <c r="C3" t="n">
-        <v>21.75062038758809</v>
+        <v>20.04728812071987</v>
       </c>
       <c r="D3" t="n">
-        <v>66.95519342963247</v>
+        <v>102.2146622276567</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.97283952611313</v>
+        <v>45.80540263704343</v>
       </c>
       <c r="C4" t="n">
-        <v>100.6723365842849</v>
+        <v>89.79849901204726</v>
       </c>
       <c r="D4" t="n">
-        <v>125.6617426481832</v>
+        <v>169.7824662247391</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.73056882734243</v>
+        <v>45.35674393620265</v>
       </c>
       <c r="C5" t="n">
-        <v>190.1154429273949</v>
+        <v>161.7920216598744</v>
       </c>
       <c r="D5" t="n">
-        <v>102.3226544751238</v>
+        <v>117.2697632722815</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.17115256237099</v>
+        <v>41.66046382971341</v>
       </c>
       <c r="C6" t="n">
-        <v>200.2117363178691</v>
+        <v>180.1261600366836</v>
       </c>
       <c r="D6" t="n">
-        <v>53.05168244208915</v>
+        <v>52.60891422747383</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.70942804173872</v>
+        <v>27.78738702100172</v>
       </c>
       <c r="C7" t="n">
-        <v>170.3175187235536</v>
+        <v>164.0294246778528</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C8" t="n">
-        <v>121.9183386518901</v>
+        <v>120.4997132192535</v>
       </c>
       <c r="D8" t="n">
-        <v>29.95803119509142</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>68.00468172547228</v>
+        <v>67.67186925373262</v>
       </c>
       <c r="D9" t="n">
-        <v>29.50937249425062</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>40.00131020953629</v>
       </c>
       <c r="D10" t="n">
         <v>30.32127784566274</v>
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2495,7 +2495,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
         <v>19.35908298004286</v>
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.581996462169111</v>
+        <v>3.255475387282424</v>
       </c>
       <c r="C2" t="n">
-        <v>3.6471927212769</v>
+        <v>2.659554530804609</v>
       </c>
       <c r="D2" t="n">
-        <v>16.14091400552181</v>
+        <v>14.77039421039326</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.57114048416017</v>
+        <v>22.91399141712056</v>
       </c>
       <c r="C3" t="n">
-        <v>26.84098223410779</v>
+        <v>22.0696883914683</v>
       </c>
       <c r="D3" t="n">
-        <v>70.50421138048469</v>
+        <v>100.3198891584603</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.80165557267569</v>
+        <v>50.13196476965913</v>
       </c>
       <c r="C4" t="n">
-        <v>93.83151858109315</v>
+        <v>84.60407190887737</v>
       </c>
       <c r="D4" t="n">
-        <v>132.5663742521511</v>
+        <v>181.6390332489279</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.25227776892498</v>
+        <v>46.48575379608648</v>
       </c>
       <c r="C5" t="n">
-        <v>221.4331946928681</v>
+        <v>188.8146272192678</v>
       </c>
       <c r="D5" t="n">
-        <v>107.673179463269</v>
+        <v>124.3138030502524</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.88560284915541</v>
+        <v>33.77113927838603</v>
       </c>
       <c r="C6" t="n">
-        <v>236.3979749487023</v>
+        <v>214.2998158738108</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>51.40136455125026</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>170.9762714331032</v>
+        <v>167.0237551758056</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>33.77604801690726</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>87.12029127486194</v>
+        <v>85.2844230679204</v>
       </c>
       <c r="D8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.29320807286708</v>
       </c>
     </row>
     <row r="9">
@@ -2747,7 +2747,7 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.28593492830985</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
         <v>31.72812230584841</v>
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.90832191507333</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>19.72429312602266</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2792,7 +2792,7 @@
         <v>15.4046032273367</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.437098712568083</v>
+        <v>4.177336481570178</v>
       </c>
       <c r="C2" t="n">
-        <v>5.089380098815464</v>
+        <v>3.84452400983051</v>
       </c>
       <c r="D2" t="n">
-        <v>17.8668264695877</v>
+        <v>13.27322896141688</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.40223882130071</v>
+        <v>17.30821202587127</v>
       </c>
       <c r="C3" t="n">
-        <v>20.43507846389736</v>
+        <v>16.22828955119978</v>
       </c>
       <c r="D3" t="n">
-        <v>67.82894888641214</v>
+        <v>90.93928984438205</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.15977250054753</v>
+        <v>47.04338649209866</v>
       </c>
       <c r="C4" t="n">
-        <v>81.46444275069608</v>
+        <v>70.29706261488862</v>
       </c>
       <c r="D4" t="n">
-        <v>136.3186139777824</v>
+        <v>188.2756477296363</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.30890034060182</v>
+        <v>58.36490101747289</v>
       </c>
       <c r="C5" t="n">
-        <v>198.7057353395545</v>
+        <v>175.143790437631</v>
       </c>
       <c r="D5" t="n">
-        <v>125.5900750657732</v>
+        <v>152.9317486290469</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.94851681768522</v>
+        <v>44.92084795551706</v>
       </c>
       <c r="C6" t="n">
-        <v>292.3880282696021</v>
+        <v>253.8269419421959</v>
       </c>
       <c r="D6" t="n">
-        <v>67.98504677138737</v>
+        <v>71.20517924131691</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>18.26541603751191</v>
       </c>
       <c r="C7" t="n">
-        <v>243.3791828736013</v>
+        <v>229.7250358029366</v>
       </c>
       <c r="D7" t="n">
-        <v>40.00425545264903</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>144.3659999094935</v>
+        <v>138.9418438435298</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>57.68749510154256</v>
+        <v>57.35468262980289</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.91359050649305</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.317906329726719</v>
+        <v>2.851977080836984</v>
       </c>
       <c r="C2" t="n">
-        <v>3.655046702910875</v>
+        <v>2.167698930976957</v>
       </c>
       <c r="D2" t="n">
-        <v>12.80788054960389</v>
+        <v>10.01186308790897</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.40085616296896</v>
+        <v>16.16938468894497</v>
       </c>
       <c r="C3" t="n">
-        <v>20.33199495495144</v>
+        <v>15.80122929985241</v>
       </c>
       <c r="D3" t="n">
-        <v>67.36752746541613</v>
+        <v>83.91488502049611</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.92254940901829</v>
+        <v>42.7551125199486</v>
       </c>
       <c r="C4" t="n">
-        <v>70.67994421954486</v>
+        <v>59.52532680389261</v>
       </c>
       <c r="D4" t="n">
-        <v>138.4755136840126</v>
+        <v>190.3687338350905</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.16855147662353</v>
+        <v>64.40264939859077</v>
       </c>
       <c r="C5" t="n">
-        <v>187.2683745850791</v>
+        <v>164.0254976870359</v>
       </c>
       <c r="D5" t="n">
-        <v>137.3955912093411</v>
+        <v>171.830391935798</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.27431818677493</v>
+        <v>53.13218575383738</v>
       </c>
       <c r="C6" t="n">
-        <v>314.7276972797383</v>
+        <v>274.5162930614932</v>
       </c>
       <c r="D6" t="n">
-        <v>81.06683493047613</v>
+        <v>87.94986808495052</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>16.34904451882213</v>
       </c>
       <c r="C7" t="n">
-        <v>302.6070401231071</v>
+        <v>280.1495613884613</v>
       </c>
       <c r="D7" t="n">
-        <v>44.43586458961913</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.506221962492859</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>191.0971906316416</v>
+        <v>179.8316357254095</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>66.34061936677394</v>
+        <v>65.56405693271472</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.737513510067607</v>
+        <v>4.993168823799278</v>
       </c>
       <c r="C2" t="n">
-        <v>14.5887708851076</v>
+        <v>10.2327563213645</v>
       </c>
       <c r="D2" t="n">
-        <v>12.43972516051134</v>
+        <v>13.19468914507713</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.75504610002381</v>
+        <v>13.05724446648258</v>
       </c>
       <c r="C3" t="n">
-        <v>17.36220814960484</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="D3" t="n">
-        <v>62.65513848503144</v>
+        <v>74.48028958268428</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.46010518258904</v>
+        <v>36.9353121291735</v>
       </c>
       <c r="C4" t="n">
-        <v>61.68222651012285</v>
+        <v>50.48932093400496</v>
       </c>
       <c r="D4" t="n">
-        <v>139.5475821770501</v>
+        <v>188.5819530133613</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.0395416167397</v>
+        <v>64.15721247252907</v>
       </c>
       <c r="C5" t="n">
-        <v>162.6510509010903</v>
+        <v>140.6108149407494</v>
       </c>
       <c r="D5" t="n">
-        <v>150.5264667536422</v>
+        <v>192.6925306510427</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.73974871404592</v>
+        <v>65.56994741894023</v>
       </c>
       <c r="C6" t="n">
-        <v>309.1327171132357</v>
+        <v>270.0886109153401</v>
       </c>
       <c r="D6" t="n">
-        <v>98.01278205348032</v>
+        <v>111.0140669008208</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.9014907388726</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="C7" t="n">
-        <v>367.1049190490098</v>
+        <v>330.5142003640269</v>
       </c>
       <c r="D7" t="n">
-        <v>52.939763203805</v>
+        <v>53.59851591335461</v>
       </c>
     </row>
     <row r="8">
@@ -3666,10 +3666,10 @@
         <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>270.0395235301276</v>
+        <v>251.9311871252953</v>
       </c>
       <c r="D8" t="n">
-        <v>36.96770980341364</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>127.578114166873</v>
+        <v>122.2531146190383</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>47.68839473378882</v>
+        <v>46.83427423109409</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.6997904911455</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.433973543006096</v>
+        <v>5.320090809313465</v>
       </c>
       <c r="C2" t="n">
-        <v>5.133558745506572</v>
+        <v>6.37743308678728</v>
       </c>
       <c r="D2" t="n">
-        <v>11.59247689174634</v>
+        <v>8.283987128434585</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.702751429791469</v>
+        <v>3.608904560811275</v>
       </c>
       <c r="C2" t="n">
-        <v>8.40277860064845</v>
+        <v>5.893431468593603</v>
       </c>
       <c r="D2" t="n">
-        <v>9.254935607934682</v>
+        <v>9.817477042468104</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5740446695439</v>
+        <v>17.72054606165493</v>
       </c>
       <c r="C3" t="n">
-        <v>31.33738671955819</v>
+        <v>22.08932334555324</v>
       </c>
       <c r="D3" t="n">
-        <v>67.23499152534281</v>
+        <v>80.06643401984863</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.46982484864026</v>
+        <v>49.71079500453725</v>
       </c>
       <c r="C4" t="n">
-        <v>90.33453325856601</v>
+        <v>74.70020106843556</v>
       </c>
       <c r="D4" t="n">
-        <v>143.3636355034575</v>
+        <v>192.4107690599239</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.26928627506667</v>
+        <v>38.11635461738242</v>
       </c>
       <c r="C5" t="n">
-        <v>254.2235680147116</v>
+        <v>221.1632140742003</v>
       </c>
       <c r="D5" t="n">
-        <v>137.6410281354028</v>
+        <v>171.9040230136165</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.15978819608075</v>
+        <v>19.68305972244431</v>
       </c>
       <c r="C6" t="n">
-        <v>299.3515647358248</v>
+        <v>267.9955248098859</v>
       </c>
       <c r="D6" t="n">
-        <v>78.32972233103602</v>
+        <v>85.09200051788805</v>
       </c>
     </row>
     <row r="7">
@@ -4274,10 +4274,10 @@
         <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>189.9004401801648</v>
+        <v>177.144592258886</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.45854259780804</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>90.04099069499621</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.45042657426681</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>36.38749691020377</v>
+        <v>35.72187196672443</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>19.3600647277471</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.99267010218054</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.52575910558656</v>
       </c>
     </row>
     <row r="12">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.706318567709961</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C2" t="n">
-        <v>5.103124566674921</v>
+        <v>4.292200962967055</v>
       </c>
       <c r="D2" t="n">
-        <v>14.25988540418492</v>
+        <v>12.54084517404875</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.54535300194249</v>
+        <v>11.30482481440202</v>
       </c>
       <c r="C3" t="n">
-        <v>12.93452600345173</v>
+        <v>16.06630117999905</v>
       </c>
       <c r="D3" t="n">
-        <v>12.87562114119692</v>
+        <v>10.09236639965721</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4557,7 +4557,7 @@
         <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39819766108588</v>
+        <v>13.39857197663392</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14350540215547</v>
+        <v>70.14546505414228</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576258548363044</v>
+        <v>1.576302585486343</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.413937678293659</v>
+        <v>4.784056562794707</v>
       </c>
       <c r="C2" t="n">
-        <v>9.231373663032759</v>
+        <v>7.36212603414683</v>
       </c>
       <c r="D2" t="n">
-        <v>24.87846857331843</v>
+        <v>15.07375425100552</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.49612674800991</v>
+        <v>19.32570355809846</v>
       </c>
       <c r="C3" t="n">
-        <v>17.49474408967816</v>
+        <v>16.65534980254714</v>
       </c>
       <c r="D3" t="n">
-        <v>21.74080291054562</v>
+        <v>18.18687622117216</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.464669763745</v>
+        <v>13.19665264048563</v>
       </c>
       <c r="C4" t="n">
-        <v>20.25443688631594</v>
+        <v>25.01493150420873</v>
       </c>
       <c r="D4" t="n">
-        <v>21.81148874525138</v>
+        <v>20.35653864755761</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,7 +4882,7 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
         <v>34.77743067523902</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>44.22773407631881</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44236840005066</v>
+        <v>15.44316591934243</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15216054765105</v>
+        <v>86.15660986580517</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251024926326455</v>
+        <v>3.251192825124723</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.487568756112171</v>
+        <v>4.781111319681966</v>
       </c>
       <c r="C2" t="n">
-        <v>6.484443586550183</v>
+        <v>8.847510310672256</v>
       </c>
       <c r="D2" t="n">
-        <v>23.14372037991431</v>
+        <v>28.38527137288803</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.68480223367454</v>
+        <v>17.76963344686727</v>
       </c>
       <c r="C3" t="n">
-        <v>28.6719417025281</v>
+        <v>23.930100291016</v>
       </c>
       <c r="D3" t="n">
-        <v>36.59955441432109</v>
+        <v>26.02613163958294</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.03594911662541</v>
+        <v>26.81447504609313</v>
       </c>
       <c r="C4" t="n">
-        <v>34.11475097487241</v>
+        <v>34.8422260237193</v>
       </c>
       <c r="D4" t="n">
-        <v>27.8099672181994</v>
+        <v>24.90006702281185</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>12.10004045484194</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C5" t="n">
-        <v>23.63557597974196</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="D5" t="n">
-        <v>30.26237298340794</v>
+        <v>29.77149913128453</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
         <v>36.6290068454485</v>
@@ -5204,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -5218,7 +5218,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
         <v>29.87458264023044</v>
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.35888735806038</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73660015442623</v>
+        <v>16.7397291003862</v>
       </c>
       <c r="C21" t="n">
-        <v>102.093260942</v>
+        <v>102.1123475123558</v>
       </c>
       <c r="D21" t="n">
-        <v>5.02098004632787</v>
+        <v>5.021918730115861</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.253331965424683</v>
+        <v>6.259623362277663</v>
       </c>
       <c r="C2" t="n">
-        <v>8.985936736971055</v>
+        <v>10.1738514591097</v>
       </c>
       <c r="D2" t="n">
-        <v>23.74062298409637</v>
+        <v>29.07740350438203</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.96812640957437</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C3" t="n">
-        <v>26.63481521621597</v>
+        <v>29.92367002544278</v>
       </c>
       <c r="D3" t="n">
-        <v>46.04887606769665</v>
+        <v>41.80772598535042</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.57122259961817</v>
+        <v>31.06446085777758</v>
       </c>
       <c r="C4" t="n">
-        <v>54.80312034646545</v>
+        <v>48.49833658979244</v>
       </c>
       <c r="D4" t="n">
-        <v>39.24536447726624</v>
+        <v>31.93232582833176</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.45180923259857</v>
+        <v>25.9181393921158</v>
       </c>
       <c r="C5" t="n">
-        <v>45.28311285838414</v>
+        <v>48.27744335633691</v>
       </c>
       <c r="D5" t="n">
-        <v>33.06035394051135</v>
+        <v>31.71045084717198</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.23021198887927</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="C6" t="n">
-        <v>25.51954982419159</v>
+        <v>29.7057220351</v>
       </c>
       <c r="D6" t="n">
-        <v>38.35982804803563</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5515,10 +5515,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
         <v>39.46527596301753</v>
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
         <v>40.38910055271378</v>
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>34.16874709860598</v>
       </c>
       <c r="D9" t="n">
         <v>41.93437143919824</v>
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5605,7 +5605,7 @@
         <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>44.07556318216055</v>
       </c>
     </row>
     <row r="16">
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06383823521628</v>
+        <v>18.06750087136144</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8450399154586</v>
+        <v>117.8689342560246</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881462184844297</v>
+        <v>6.882857474804355</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.976299186377835</v>
+        <v>7.392560212978482</v>
       </c>
       <c r="C2" t="n">
-        <v>10.53807985738526</v>
+        <v>6.403940274801944</v>
       </c>
       <c r="D2" t="n">
-        <v>30.89363675723863</v>
+        <v>37.46447414176253</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.22690689286803</v>
+        <v>17.36711688812607</v>
       </c>
       <c r="C3" t="n">
-        <v>29.47697482001048</v>
+        <v>33.28124717396687</v>
       </c>
       <c r="D3" t="n">
-        <v>50.66309027765665</v>
+        <v>51.36994862471436</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.92635322664826</v>
+        <v>23.21538796232432</v>
       </c>
       <c r="C4" t="n">
-        <v>50.99982974021331</v>
+        <v>52.95252592396021</v>
       </c>
       <c r="D4" t="n">
-        <v>46.00960615952677</v>
+        <v>39.24536447726624</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.57390580082366</v>
+        <v>22.40839134943345</v>
       </c>
       <c r="C5" t="n">
-        <v>56.40140560897927</v>
+        <v>51.98354093986863</v>
       </c>
       <c r="D5" t="n">
-        <v>31.63681976935347</v>
+        <v>28.81429511964389</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.39751000922872</v>
+        <v>12.51826497685108</v>
       </c>
       <c r="C6" t="n">
-        <v>33.73088762251191</v>
+        <v>36.79001346894498</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.509568116233099</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>18.68462230722529</v>
+        <v>20.54110721595601</v>
       </c>
       <c r="D7" t="n">
         <v>30.72183090899544</v>
@@ -5843,7 +5843,7 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
         <v>30.37527396939631</v>
@@ -5857,7 +5857,7 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
         <v>29.95312245657017</v>
@@ -5868,7 +5868,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
         <v>21.49536598448391</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060454745546799</v>
+        <v>7.061629794997511</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19176323950123</v>
+        <v>66.20277932810167</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295341059160099</v>
+        <v>5.296222346248133</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.472662614099221</v>
+        <v>5.644067551714913</v>
       </c>
       <c r="C2" t="n">
-        <v>9.64665294192916</v>
+        <v>5.822745633887832</v>
       </c>
       <c r="D2" t="n">
-        <v>22.95129782988193</v>
+        <v>44.64301335521521</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.88668240785089</v>
+        <v>22.62437584436775</v>
       </c>
       <c r="C3" t="n">
-        <v>37.02170592714722</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="D3" t="n">
-        <v>64.37319696746336</v>
+        <v>70.42567156414495</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.01867856857647</v>
+        <v>30.08173140582652</v>
       </c>
       <c r="C4" t="n">
-        <v>65.43446623575416</v>
+        <v>72.14765703739384</v>
       </c>
       <c r="D4" t="n">
-        <v>61.43973482717389</v>
+        <v>56.6792402092811</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.47068342315751</v>
+        <v>29.94330497952772</v>
       </c>
       <c r="C5" t="n">
-        <v>79.61973881441634</v>
+        <v>80.08606897393356</v>
       </c>
       <c r="D5" t="n">
-        <v>42.11697651218817</v>
+        <v>37.33095645398497</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.93715245139498</v>
+        <v>22.62143060125501</v>
       </c>
       <c r="C6" t="n">
-        <v>66.25422556880025</v>
+        <v>63.75862290460487</v>
       </c>
       <c r="D6" t="n">
-        <v>34.73717901936489</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.89936301254809</v>
+        <v>10.95924962250714</v>
       </c>
       <c r="C7" t="n">
-        <v>36.53083207502382</v>
+        <v>39.40538935305847</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -6154,7 +6154,7 @@
         <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>22.61455836732527</v>
+        <v>24.11663235482289</v>
       </c>
       <c r="D8" t="n">
         <v>32.3780392860598</v>
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
         <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -6238,7 +6238,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.282430528482158</v>
+        <v>7.283121331925228</v>
       </c>
       <c r="C21" t="n">
-        <v>75.5552167330024</v>
+        <v>75.56238381872426</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372126712421888</v>
+        <v>6.372731165434574</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.718279466610171</v>
+        <v>5.98669750049705</v>
       </c>
       <c r="C2" t="n">
-        <v>7.930557954905733</v>
+        <v>6.493279315888404</v>
       </c>
       <c r="D2" t="n">
-        <v>19.30214161319654</v>
+        <v>45.52560454133309</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.76043786463055</v>
+        <v>21.08303194870025</v>
       </c>
       <c r="C3" t="n">
-        <v>37.3358651925062</v>
+        <v>24.77931205518949</v>
       </c>
       <c r="D3" t="n">
-        <v>67.79949645528473</v>
+        <v>89.80046250745575</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.86775146402972</v>
+        <v>37.63726173770997</v>
       </c>
       <c r="C4" t="n">
-        <v>81.52825635147212</v>
+        <v>70.93519862264904</v>
       </c>
       <c r="D4" t="n">
-        <v>79.90739089176064</v>
+        <v>79.21820400337938</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.9993056563988</v>
+        <v>38.36179154344412</v>
       </c>
       <c r="C5" t="n">
-        <v>103.2307711015521</v>
+        <v>109.1703447122453</v>
       </c>
       <c r="D5" t="n">
-        <v>54.29064804484862</v>
+        <v>48.89103567149117</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.19503330244241</v>
+        <v>32.12082138754715</v>
       </c>
       <c r="C6" t="n">
-        <v>99.42159000907451</v>
+        <v>98.69706020334036</v>
       </c>
       <c r="D6" t="n">
-        <v>40.49316580936395</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>68.33062196328224</v>
+        <v>68.15096213340507</v>
       </c>
       <c r="D7" t="n">
-        <v>35.93196597543326</v>
+        <v>35.51275970571987</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>36.96770980341364</v>
+        <v>39.22082078466007</v>
       </c>
       <c r="D8" t="n">
         <v>33.96356182841841</v>
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>26.5140602485936</v>
+        <v>27.62343515439249</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>34.06370009425158</v>
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
         <v>23.41468274628643</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
         <v>30.72870314292517</v>
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.491076028076905</v>
+        <v>7.490029886821772</v>
       </c>
       <c r="C21" t="n">
-        <v>85.21098981937479</v>
+        <v>85.19908996259765</v>
       </c>
       <c r="D21" t="n">
-        <v>7.491076028076905</v>
+        <v>7.490029886821772</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_5_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_5_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626192125</v>
+        <v>10.84497652550641</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907169697234</v>
+        <v>37.78907261542877</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.056802498126073</v>
+        <v>1.146681318560274</v>
       </c>
       <c r="C2" t="n">
-        <v>9.53866069446201</v>
+        <v>2.16377194015997</v>
       </c>
       <c r="D2" t="n">
-        <v>36.92353115672254</v>
+        <v>13.35176877775662</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.59215809657685</v>
+        <v>10.06291396852981</v>
       </c>
       <c r="C3" t="n">
-        <v>24.94130042639022</v>
+        <v>37.44385743997335</v>
       </c>
       <c r="D3" t="n">
-        <v>103.4663905505714</v>
+        <v>56.53885028757381</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.82419471214436</v>
+        <v>16.73192612347839</v>
       </c>
       <c r="C4" t="n">
-        <v>65.45999167606458</v>
+        <v>143.2360083019054</v>
       </c>
       <c r="D4" t="n">
-        <v>102.7016090889631</v>
+        <v>68.34436643114171</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.07480241863456</v>
+        <v>14.7753029489145</v>
       </c>
       <c r="C5" t="n">
-        <v>120.4849870036898</v>
+        <v>165.203594932132</v>
       </c>
       <c r="D5" t="n">
-        <v>65.26167863980673</v>
+        <v>45.23402547317179</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.18373535607696</v>
+        <v>9.660397409788615</v>
       </c>
       <c r="C6" t="n">
-        <v>135.2455637370406</v>
+        <v>101.4341728027805</v>
       </c>
       <c r="D6" t="n">
-        <v>44.39757642915352</v>
+        <v>29.78622534684823</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.62579956042849</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>105.87952640761</v>
+        <v>54.67647489261761</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.0207398749762</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>64.83952712698058</v>
+        <v>30.70906818884022</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>30.84062238120929</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.680927238967817</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.09135867735574</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.641043143838793</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.598146393793566</v>
+        <v>1.20951317163207</v>
       </c>
       <c r="C2" t="n">
-        <v>5.781512230309467</v>
+        <v>3.021819433671682</v>
       </c>
       <c r="D2" t="n">
-        <v>30.21230385049135</v>
+        <v>13.72581465307466</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.0991408225957</v>
+        <v>6.823146544515332</v>
       </c>
       <c r="C3" t="n">
-        <v>30.90541772968959</v>
+        <v>21.01921834792421</v>
       </c>
       <c r="D3" t="n">
-        <v>107.5455522617168</v>
+        <v>54.65389469541994</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.41578766717769</v>
+        <v>18.28897798241383</v>
       </c>
       <c r="C4" t="n">
-        <v>63.80083805588747</v>
+        <v>116.0258889310008</v>
       </c>
       <c r="D4" t="n">
-        <v>126.7210484210655</v>
+        <v>79.19267856306897</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.76264770641309</v>
+        <v>19.83130362578557</v>
       </c>
       <c r="C5" t="n">
-        <v>119.2578023733813</v>
+        <v>219.4451555917683</v>
       </c>
       <c r="D5" t="n">
-        <v>82.95768100885549</v>
+        <v>58.73305640656545</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.64287448649497</v>
+        <v>14.53084777055704</v>
       </c>
       <c r="C6" t="n">
-        <v>161.4493917110922</v>
+        <v>182.7022660126272</v>
       </c>
       <c r="D6" t="n">
-        <v>53.41394734495622</v>
+        <v>36.91076843656734</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.62686342359076</v>
+        <v>8.26435217434965</v>
       </c>
       <c r="C7" t="n">
-        <v>145.883781860259</v>
+        <v>99.47165914199108</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>31.32069700858599</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.03041848329842</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>99.63757450400877</v>
+        <v>50.5698242457532</v>
       </c>
       <c r="D8" t="n">
-        <v>38.13598957146735</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>56.91093266748334</v>
+        <v>35.38905949498476</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>36.16562192904399</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
+        <v>33.88011327355743</v>
+      </c>
+      <c r="D10" t="n">
         <v>37.72365553568369</v>
-      </c>
-      <c r="D10" t="n">
-        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.855765355942813</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1249496272566</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.819706694928517</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.724791847641404</v>
+        <v>0.6607162049581033</v>
       </c>
       <c r="C2" t="n">
-        <v>7.600690726278806</v>
+        <v>1.324377653028947</v>
       </c>
       <c r="D2" t="n">
-        <v>33.27044794922016</v>
+        <v>9.354092126063609</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.58296251434013</v>
+        <v>6.371542600561799</v>
       </c>
       <c r="C3" t="n">
-        <v>26.78698611037422</v>
+        <v>18.06906649666254</v>
       </c>
       <c r="D3" t="n">
-        <v>105.8814899030185</v>
+        <v>54.92878405260904</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.05392367493812</v>
+        <v>19.76945352041802</v>
       </c>
       <c r="C4" t="n">
-        <v>68.84211251719483</v>
+        <v>102.3570156447725</v>
       </c>
       <c r="D4" t="n">
-        <v>143.6571780670273</v>
+        <v>87.22042954069512</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.21701696703012</v>
+        <v>19.53677931451153</v>
       </c>
       <c r="C5" t="n">
-        <v>117.048870038826</v>
+        <v>249.5602664195393</v>
       </c>
       <c r="D5" t="n">
-        <v>103.5743827980385</v>
+        <v>65.87527095496098</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>58.6064109527176</v>
+        <v>11.43147026824986</v>
       </c>
       <c r="C6" t="n">
-        <v>173.7663984085727</v>
+        <v>225.5300278626901</v>
       </c>
       <c r="D6" t="n">
-        <v>63.27560303411543</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>47.66974152740813</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>181.3366549560199</v>
+        <v>92.64458560665875</v>
       </c>
       <c r="D7" t="n">
-        <v>46.17257627843174</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.95803119509142</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>138.190806849781</v>
+        <v>42.89255719854314</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.42031119060464</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>84.97811778419538</v>
+        <v>25.84843530511426</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16405934426299</v>
+        <v>39.71562162760046</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.78314123501524</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>33.1958351236974</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.014681653236002</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.2000375253405</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0201872731995</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.119053514121122</v>
+        <v>1.04948829583984</v>
       </c>
       <c r="C2" t="n">
-        <v>5.228788272818512</v>
+        <v>2.663481521621597</v>
       </c>
       <c r="D2" t="n">
-        <v>27.63227088373073</v>
+        <v>9.120436172452868</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.08289307998001</v>
+        <v>4.309872421643497</v>
       </c>
       <c r="C3" t="n">
-        <v>41.1548637620263</v>
+        <v>11.01030050312798</v>
       </c>
       <c r="D3" t="n">
-        <v>113.5342132576224</v>
+        <v>49.97095814616264</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.04871183678062</v>
+        <v>16.36180723897734</v>
       </c>
       <c r="C4" t="n">
-        <v>95.43962132064942</v>
+        <v>73.02828472810323</v>
       </c>
       <c r="D4" t="n">
-        <v>130.9965596730604</v>
+        <v>94.16334930512858</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.011266555299</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="C5" t="n">
-        <v>103.8198197241002</v>
+        <v>221.4577383854743</v>
       </c>
       <c r="D5" t="n">
-        <v>65.62983402889928</v>
+        <v>81.11690406339272</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.58496706747763</v>
+        <v>17.54972196111598</v>
       </c>
       <c r="C6" t="n">
-        <v>119.4266629785118</v>
+        <v>310.6220283805781</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>47.13468902859362</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.82246789644735</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>97.13608135358791</v>
+        <v>195.8292145661113</v>
       </c>
       <c r="D7" t="n">
-        <v>27.96704685087888</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>62.58641614573416</v>
+        <v>77.85750168529329</v>
       </c>
       <c r="D8" t="n">
-        <v>27.37112599440107</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>37.27499683484289</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>31.74481201682062</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.58823110575986</v>
-      </c>
-      <c r="D14" t="n">
-        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.65030219530566</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.74984392852887</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.925428232206248</v>
+        <v>0.5861033794353457</v>
       </c>
       <c r="C2" t="n">
-        <v>2.440624792757571</v>
+        <v>2.816634163484099</v>
       </c>
       <c r="D2" t="n">
-        <v>19.74294633240336</v>
+        <v>7.132397071353077</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.69648539513427</v>
+        <v>4.054618018539327</v>
       </c>
       <c r="C3" t="n">
-        <v>31.396291581813</v>
+        <v>10.926851948267</v>
       </c>
       <c r="D3" t="n">
-        <v>111.4332731705342</v>
+        <v>46.61338099763856</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.39477005476101</v>
+        <v>13.464669763745</v>
       </c>
       <c r="C4" t="n">
-        <v>101.412574353287</v>
+        <v>53.9990689766873</v>
       </c>
       <c r="D4" t="n">
-        <v>151.9146580074472</v>
+        <v>97.3540293439307</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.76645152404306</v>
+        <v>25.74633354387261</v>
       </c>
       <c r="C5" t="n">
-        <v>138.7700379952867</v>
+        <v>193.453385121834</v>
       </c>
       <c r="D5" t="n">
-        <v>88.74999246391167</v>
+        <v>92.67698328089891</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.30070220160257</v>
+        <v>21.85664913964674</v>
       </c>
       <c r="C6" t="n">
-        <v>142.6116167620044</v>
+        <v>341.1730351890346</v>
       </c>
       <c r="D6" t="n">
-        <v>37.55479493055324</v>
+        <v>55.70829172978102</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.50496247734813</v>
+        <v>7.845145904636261</v>
       </c>
       <c r="C7" t="n">
-        <v>126.9596131131975</v>
+        <v>282.2455927370282</v>
       </c>
       <c r="D7" t="n">
-        <v>30.3625112492411</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>82.94786353181301</v>
+        <v>122.2521328713341</v>
       </c>
       <c r="D8" t="n">
-        <v>28.12216298814988</v>
+        <v>38.88702656521616</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>47.37030847761284</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>32.87382187670443</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.09163099832699</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.436918786118836</v>
+        <v>0.4673119072214817</v>
       </c>
       <c r="C2" t="n">
-        <v>5.594980166502572</v>
+        <v>13.53044685992954</v>
       </c>
       <c r="D2" t="n">
-        <v>21.20575041173111</v>
+        <v>17.22181822789755</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.69800692218626</v>
+        <v>3.043417883165112</v>
       </c>
       <c r="C3" t="n">
-        <v>20.04728812071987</v>
+        <v>10.97103059495811</v>
       </c>
       <c r="D3" t="n">
-        <v>102.2146622276567</v>
+        <v>42.15133768183681</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.80540263704343</v>
+        <v>10.72068493037517</v>
       </c>
       <c r="C4" t="n">
-        <v>89.79849901204726</v>
+        <v>41.08319617961627</v>
       </c>
       <c r="D4" t="n">
-        <v>169.7824662247391</v>
+        <v>98.05597895246717</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.35674393620265</v>
+        <v>23.8564692131975</v>
       </c>
       <c r="C5" t="n">
-        <v>161.7920216598744</v>
+        <v>149.8392433606695</v>
       </c>
       <c r="D5" t="n">
-        <v>117.2697632722815</v>
+        <v>102.5680914011855</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.66046382971341</v>
+        <v>27.16986771503048</v>
       </c>
       <c r="C6" t="n">
-        <v>180.1261600366836</v>
+        <v>331.2711278440013</v>
       </c>
       <c r="D6" t="n">
-        <v>52.60891422747383</v>
+        <v>68.83033154474388</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.78738702100172</v>
+        <v>14.49255961009142</v>
       </c>
       <c r="C7" t="n">
-        <v>164.0294246778528</v>
+        <v>372.6743737752019</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>45.27427712904591</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>120.4997132192535</v>
+        <v>226.9800692218625</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>40.97324043674063</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>67.67186925373262</v>
+        <v>88.41717999217197</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>41.3796839862988</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>40.00131020953629</v>
+        <v>41.14013754646259</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>17.20807376003809</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.255475387282424</v>
+        <v>0.321031499288707</v>
       </c>
       <c r="C2" t="n">
-        <v>2.659554530804609</v>
+        <v>7.360162538738337</v>
       </c>
       <c r="D2" t="n">
-        <v>14.77039421039326</v>
+        <v>12.53691818323177</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.91399141712056</v>
+        <v>4.084070449666732</v>
       </c>
       <c r="C3" t="n">
-        <v>22.0696883914683</v>
+        <v>26.37465207459056</v>
       </c>
       <c r="D3" t="n">
-        <v>100.3198891584603</v>
+        <v>48.83703954775758</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>50.13196476965913</v>
+        <v>16.82126516456485</v>
       </c>
       <c r="C4" t="n">
-        <v>84.60407190887737</v>
+        <v>64.96224559001143</v>
       </c>
       <c r="D4" t="n">
-        <v>181.6390332489279</v>
+        <v>100.7616756253714</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.48575379608648</v>
+        <v>16.39518666092174</v>
       </c>
       <c r="C5" t="n">
-        <v>188.8146272192678</v>
+        <v>254.5426360185918</v>
       </c>
       <c r="D5" t="n">
-        <v>124.3138030502524</v>
+        <v>94.98409038587891</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.77113927838603</v>
+        <v>8.976119259928589</v>
       </c>
       <c r="C6" t="n">
-        <v>214.2998158738108</v>
+        <v>320.1214191668702</v>
       </c>
       <c r="D6" t="n">
-        <v>51.40136455125026</v>
+        <v>60.01521890831177</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>167.0237551758056</v>
+        <v>159.5978155408827</v>
       </c>
       <c r="D7" t="n">
-        <v>33.77604801690726</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>85.2844230679204</v>
+        <v>65.17332134642452</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>30.50780990946962</v>
+        <v>31.39530983410874</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>24.05772749256809</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.72429312602266</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.4046032273367</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.04880964777186</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>33.68376373270807</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.177336481570178</v>
+        <v>0.212057504117311</v>
       </c>
       <c r="C2" t="n">
-        <v>3.84452400983051</v>
+        <v>3.750276230222815</v>
       </c>
       <c r="D2" t="n">
-        <v>13.27322896141688</v>
+        <v>8.681594948654544</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.30821202587127</v>
+        <v>2.596722677732814</v>
       </c>
       <c r="C3" t="n">
-        <v>16.22828955119978</v>
+        <v>27.92581344730052</v>
       </c>
       <c r="D3" t="n">
-        <v>90.93928984438205</v>
+        <v>47.7865695042135</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.04338649209866</v>
+        <v>11.75446526294706</v>
       </c>
       <c r="C4" t="n">
-        <v>70.29706261488862</v>
+        <v>62.69048140238433</v>
       </c>
       <c r="D4" t="n">
-        <v>188.2756477296363</v>
+        <v>97.71138550827655</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.36490101747289</v>
+        <v>15.90431280879833</v>
       </c>
       <c r="C5" t="n">
-        <v>175.143790437631</v>
+        <v>173.2048387217436</v>
       </c>
       <c r="D5" t="n">
-        <v>152.9317486290469</v>
+        <v>96.55488671267382</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.92084795551706</v>
+        <v>9.137125883425066</v>
       </c>
       <c r="C6" t="n">
-        <v>253.8269419421959</v>
+        <v>296.735207104007</v>
       </c>
       <c r="D6" t="n">
-        <v>71.20517924131691</v>
+        <v>61.98755004614362</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.26541603751191</v>
+        <v>3.054217107911827</v>
       </c>
       <c r="C7" t="n">
-        <v>229.7250358029366</v>
+        <v>210.681093835957</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>138.9418438435298</v>
+        <v>78.02439879501526</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>26.36974333606933</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>57.35468262980289</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>20.63437324785945</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>17.22476347101029</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>12.9718324162131</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.91359050649305</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.851977080836984</v>
+        <v>0.4084070449666731</v>
       </c>
       <c r="C2" t="n">
-        <v>2.167698930976957</v>
+        <v>10.00499085397924</v>
       </c>
       <c r="D2" t="n">
-        <v>10.01186308790897</v>
+        <v>10.6038569535698</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.16938468894497</v>
+        <v>1.570796326794897</v>
       </c>
       <c r="C3" t="n">
-        <v>15.80122929985241</v>
+        <v>20.07674055184727</v>
       </c>
       <c r="D3" t="n">
-        <v>83.91488502049611</v>
+        <v>43.75649517828034</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.7551125199486</v>
+        <v>8.308530821040756</v>
       </c>
       <c r="C4" t="n">
-        <v>59.52532680389261</v>
+        <v>66.81284001251667</v>
       </c>
       <c r="D4" t="n">
-        <v>190.3687338350905</v>
+        <v>99.57474265093698</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.40264939859077</v>
+        <v>17.13149743910684</v>
       </c>
       <c r="C5" t="n">
-        <v>164.0254976870359</v>
+        <v>143.4578832830652</v>
       </c>
       <c r="D5" t="n">
-        <v>171.830391935798</v>
+        <v>109.3912379457009</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.13218575383738</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="C6" t="n">
-        <v>274.5162930614932</v>
+        <v>287.1955646618407</v>
       </c>
       <c r="D6" t="n">
-        <v>87.94986808495052</v>
+        <v>76.84041106369361</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.34904451882213</v>
+        <v>6.587527095496098</v>
       </c>
       <c r="C7" t="n">
-        <v>280.1495613884613</v>
+        <v>325.7232715673025</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>179.8316357254095</v>
+        <v>177.9957675184679</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>65.56405693271472</v>
+        <v>62.01405723415825</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>22.2984356065578</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>16.34806277111788</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.993168823799278</v>
+        <v>0.3013965452037708</v>
       </c>
       <c r="C2" t="n">
-        <v>10.2327563213645</v>
+        <v>11.66610796956485</v>
       </c>
       <c r="D2" t="n">
-        <v>13.19468914507713</v>
+        <v>18.18491272576367</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.05724446648258</v>
+        <v>1.462804079327747</v>
       </c>
       <c r="C3" t="n">
-        <v>12.30620747273377</v>
+        <v>30.06111470403734</v>
       </c>
       <c r="D3" t="n">
-        <v>74.48028958268428</v>
+        <v>42.07770660401829</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.9353121291735</v>
+        <v>5.66664774891259</v>
       </c>
       <c r="C4" t="n">
-        <v>50.48932093400496</v>
+        <v>58.12142758681967</v>
       </c>
       <c r="D4" t="n">
-        <v>188.5819530133613</v>
+        <v>98.98765752379741</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>64.15721247252907</v>
+        <v>15.06982726018854</v>
       </c>
       <c r="C5" t="n">
-        <v>140.6108149407494</v>
+        <v>133.2722508515045</v>
       </c>
       <c r="D5" t="n">
-        <v>192.6925306510427</v>
+        <v>119.4541519142307</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.56994741894023</v>
+        <v>18.99878157258428</v>
       </c>
       <c r="C6" t="n">
-        <v>270.0886109153401</v>
+        <v>260.3879618496773</v>
       </c>
       <c r="D6" t="n">
-        <v>111.0140669008208</v>
+        <v>90.80773565201298</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.73990327829938</v>
+        <v>11.73777555197486</v>
       </c>
       <c r="C7" t="n">
-        <v>330.5142003640269</v>
+        <v>368.1828780282728</v>
       </c>
       <c r="D7" t="n">
-        <v>53.59851591335461</v>
+        <v>53.17930964364123</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>251.9311871252953</v>
+        <v>299.5803119509142</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>122.2531146190383</v>
+        <v>135.565613488625</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>24.07343545583603</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>46.83427423109409</v>
+        <v>47.40368789955724</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.6997904911455</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.883434065101886</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.320090809313465</v>
+        <v>3.027709919897163</v>
       </c>
       <c r="C2" t="n">
-        <v>6.37743308678728</v>
+        <v>17.0990997648667</v>
       </c>
       <c r="D2" t="n">
-        <v>8.283987128434585</v>
+        <v>15.32999040181394</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.608904560811275</v>
+        <v>0.2228567288640259</v>
       </c>
       <c r="C2" t="n">
-        <v>5.893431468593603</v>
+        <v>26.05362057530185</v>
       </c>
       <c r="D2" t="n">
-        <v>9.817477042468104</v>
+        <v>16.12716953766235</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.72054606165493</v>
+        <v>1.227184630308513</v>
       </c>
       <c r="C3" t="n">
-        <v>22.08932334555324</v>
+        <v>37.51257977927062</v>
       </c>
       <c r="D3" t="n">
-        <v>80.06643401984863</v>
+        <v>45.5678196926157</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.71079500453725</v>
+        <v>4.301036692305276</v>
       </c>
       <c r="C4" t="n">
-        <v>74.70020106843556</v>
+        <v>65.19197455280519</v>
       </c>
       <c r="D4" t="n">
-        <v>192.4107690599239</v>
+        <v>97.57099558656925</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.11635461738242</v>
+        <v>12.34547738090364</v>
       </c>
       <c r="C5" t="n">
-        <v>221.1632140742003</v>
+        <v>121.1967540892688</v>
       </c>
       <c r="D5" t="n">
-        <v>171.9040230136165</v>
+        <v>124.8783079801943</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.68305972244431</v>
+        <v>19.80381469006666</v>
       </c>
       <c r="C6" t="n">
-        <v>267.9955248098859</v>
+        <v>238.2092994630376</v>
       </c>
       <c r="D6" t="n">
-        <v>85.09200051788805</v>
+        <v>104.7348085844582</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>16.10949807898591</v>
       </c>
       <c r="C7" t="n">
-        <v>177.144592258886</v>
+        <v>375.9082507129909</v>
       </c>
       <c r="D7" t="n">
-        <v>32.45854259780804</v>
+        <v>63.30014672672159</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>90.04099069499621</v>
+        <v>380.1916159466197</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>35.72187196672443</v>
+        <v>235.8531049728452</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>26.29218526743382</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>93.24148821084083</v>
       </c>
       <c r="D10" t="n">
-        <v>19.3600647277471</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>34.65078522139116</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.97067074205961</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.159886007071988</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C2" t="n">
-        <v>4.292200962967055</v>
+        <v>8.353691215436109</v>
       </c>
       <c r="D2" t="n">
-        <v>12.54084517404875</v>
+        <v>14.73505129304038</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.30482481440202</v>
+        <v>4.89401230567035</v>
       </c>
       <c r="C3" t="n">
-        <v>16.06630117999905</v>
+        <v>33.76230354904781</v>
       </c>
       <c r="D3" t="n">
-        <v>10.09236639965721</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.657010198319369</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.675483478250811</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39857197663392</v>
+        <v>11.67672708649437</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14546505414228</v>
+        <v>59.94053237733779</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576302585486343</v>
+        <v>0.7784484724329582</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.784056562794707</v>
+        <v>2.557452769562941</v>
       </c>
       <c r="C2" t="n">
-        <v>7.36212603414683</v>
+        <v>6.685701865920779</v>
       </c>
       <c r="D2" t="n">
-        <v>15.07375425100552</v>
+        <v>17.05982985669683</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.32570355809846</v>
+        <v>12.64981916922015</v>
       </c>
       <c r="C3" t="n">
-        <v>16.65534980254714</v>
+        <v>33.38433068291279</v>
       </c>
       <c r="D3" t="n">
-        <v>18.18687622117216</v>
+        <v>23.03670988015141</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.19665264048563</v>
+        <v>6.228207435741766</v>
       </c>
       <c r="C4" t="n">
-        <v>25.01493150420873</v>
+        <v>54.54786594336128</v>
       </c>
       <c r="D4" t="n">
-        <v>20.35653864755761</v>
+        <v>21.3775562599743</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.474225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.707300315414209</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44316591934243</v>
+        <v>13.62515129485775</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15660986580517</v>
+        <v>73.73611288981841</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251192825124723</v>
+        <v>1.602958975865618</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.781111319681966</v>
+        <v>2.507383636646354</v>
       </c>
       <c r="C2" t="n">
-        <v>8.847510310672256</v>
+        <v>13.03073727846791</v>
       </c>
       <c r="D2" t="n">
-        <v>28.38527137288803</v>
+        <v>17.93162181806799</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.76963344686727</v>
+        <v>10.4948829583984</v>
       </c>
       <c r="C3" t="n">
-        <v>23.930100291016</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D3" t="n">
-        <v>26.02613163958294</v>
+        <v>31.79880814055419</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.81447504609313</v>
+        <v>16.93612964596173</v>
       </c>
       <c r="C4" t="n">
-        <v>34.8422260237193</v>
+        <v>72.60711496298136</v>
       </c>
       <c r="D4" t="n">
-        <v>24.90006702281185</v>
+        <v>28.48639138642545</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.90369091399258</v>
+        <v>6.258641614573418</v>
       </c>
       <c r="C5" t="n">
-        <v>28.59340188618836</v>
+        <v>62.48824137530949</v>
       </c>
       <c r="D5" t="n">
-        <v>29.77149913128453</v>
+        <v>27.63619787454772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>31.95981476405067</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.7397291003862</v>
+        <v>14.8308048004815</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1123475123558</v>
+        <v>87.3369616028355</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021918730115861</v>
+        <v>2.47180080008025</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.259623362277663</v>
+        <v>2.062651926622549</v>
       </c>
       <c r="C2" t="n">
-        <v>10.1738514591097</v>
+        <v>13.313480617291</v>
       </c>
       <c r="D2" t="n">
-        <v>29.07740350438203</v>
+        <v>19.36399171856409</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.00877897607599</v>
+        <v>9.47386534598172</v>
       </c>
       <c r="C3" t="n">
-        <v>29.92367002544278</v>
+        <v>41.82245220091412</v>
       </c>
       <c r="D3" t="n">
-        <v>41.80772598535042</v>
+        <v>38.76430810218531</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.06446085777758</v>
+        <v>19.02921575141593</v>
       </c>
       <c r="C4" t="n">
-        <v>48.49833658979244</v>
+        <v>71.59886007071988</v>
       </c>
       <c r="D4" t="n">
-        <v>31.93232582833176</v>
+        <v>38.02014334236623</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.9181393921158</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="C5" t="n">
-        <v>48.27744335633691</v>
+        <v>103.3780332571892</v>
       </c>
       <c r="D5" t="n">
-        <v>31.71045084717198</v>
+        <v>31.73499453977815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>6.561019907481435</v>
       </c>
       <c r="C6" t="n">
-        <v>29.7057220351</v>
+        <v>58.96867585558468</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>33.48937768726721</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.347980655659875</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06750087136144</v>
+        <v>16.0645128253705</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8689342560246</v>
+        <v>100.6145803273205</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882857474804355</v>
+        <v>3.382002700078</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.392560212978482</v>
+        <v>2.743003085665588</v>
       </c>
       <c r="C2" t="n">
-        <v>6.403940274801944</v>
+        <v>7.810784734987623</v>
       </c>
       <c r="D2" t="n">
-        <v>37.46447414176253</v>
+        <v>21.07910495788326</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.36711688812607</v>
+        <v>8.153414683769761</v>
       </c>
       <c r="C3" t="n">
-        <v>33.28124717396687</v>
+        <v>47.3546005143449</v>
       </c>
       <c r="D3" t="n">
-        <v>51.36994862471436</v>
+        <v>44.85605260703677</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.21538796232432</v>
+        <v>18.72291046769092</v>
       </c>
       <c r="C4" t="n">
-        <v>52.95252592396021</v>
+        <v>89.70915997096078</v>
       </c>
       <c r="D4" t="n">
-        <v>39.24536447726624</v>
+        <v>48.3068957874643</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.40839134943345</v>
+        <v>22.38384765682728</v>
       </c>
       <c r="C5" t="n">
-        <v>51.98354093986863</v>
+        <v>118.6687537508332</v>
       </c>
       <c r="D5" t="n">
-        <v>28.81429511964389</v>
+        <v>37.92000507653306</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.51826497685108</v>
+        <v>13.84656962069702</v>
       </c>
       <c r="C6" t="n">
-        <v>36.79001346894498</v>
+        <v>112.4631265122891</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>35.70321876034376</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>7.246279805045708</v>
       </c>
       <c r="C7" t="n">
-        <v>20.54110721595601</v>
+        <v>51.08327829507428</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.12969817461437</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>5.858088551240717</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061629794997511</v>
+        <v>17.31846457656504</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20277932810167</v>
+        <v>113.435942976501</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296222346248133</v>
+        <v>4.32961614414126</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.644067551714913</v>
+        <v>2.490693925674158</v>
       </c>
       <c r="C2" t="n">
-        <v>5.822745633887832</v>
+        <v>7.872634840355172</v>
       </c>
       <c r="D2" t="n">
-        <v>44.64301335521521</v>
+        <v>22.44766125760332</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.62437584436775</v>
+        <v>8.634471058850698</v>
       </c>
       <c r="C3" t="n">
-        <v>27.95526587842792</v>
+        <v>38.20471191076463</v>
       </c>
       <c r="D3" t="n">
-        <v>70.42567156414495</v>
+        <v>50.07404165510857</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.08173140582652</v>
+        <v>16.98718052658256</v>
       </c>
       <c r="C4" t="n">
-        <v>72.14765703739384</v>
+        <v>104.1948473471225</v>
       </c>
       <c r="D4" t="n">
-        <v>56.6792402092811</v>
+        <v>57.52157973952487</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.94330497952772</v>
+        <v>25.18182861393069</v>
       </c>
       <c r="C5" t="n">
-        <v>80.08606897393356</v>
+        <v>140.3899217072939</v>
       </c>
       <c r="D5" t="n">
-        <v>37.33095645398497</v>
+        <v>45.7248993252952</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.62143060125501</v>
+        <v>21.1321193339126</v>
       </c>
       <c r="C6" t="n">
-        <v>63.75862290460487</v>
+        <v>149.1726366694859</v>
       </c>
       <c r="D6" t="n">
-        <v>33.52962934314132</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.95924962250714</v>
+        <v>11.43834250217959</v>
       </c>
       <c r="C7" t="n">
-        <v>39.40538935305847</v>
+        <v>103.4241753992887</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>24.11663235482289</v>
+        <v>44.6449768506237</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.61718481526852</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.04999668412111</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.283121331925228</v>
+        <v>17.70032321902591</v>
       </c>
       <c r="C21" t="n">
-        <v>75.56238381872426</v>
+        <v>126.5573110160353</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372731165434574</v>
+        <v>5.310096965707775</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.98669750049705</v>
+        <v>2.301216618754523</v>
       </c>
       <c r="C2" t="n">
-        <v>6.493279315888404</v>
+        <v>5.038329218194631</v>
       </c>
       <c r="D2" t="n">
-        <v>45.52560454133309</v>
+        <v>17.88646142367264</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.08303194870025</v>
+        <v>11.3735471536993</v>
       </c>
       <c r="C3" t="n">
-        <v>24.77931205518949</v>
+        <v>57.20643872646164</v>
       </c>
       <c r="D3" t="n">
-        <v>89.80046250745575</v>
+        <v>54.79624811253572</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.63726173770997</v>
+        <v>12.09905870713769</v>
       </c>
       <c r="C4" t="n">
-        <v>70.93519862264904</v>
+        <v>133.0896457785146</v>
       </c>
       <c r="D4" t="n">
-        <v>79.21820400337938</v>
+        <v>54.62444226429253</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.36179154344412</v>
+        <v>11.90369091399258</v>
       </c>
       <c r="C5" t="n">
-        <v>109.1703447122453</v>
+        <v>89.11814785300422</v>
       </c>
       <c r="D5" t="n">
-        <v>48.89103567149117</v>
+        <v>36.42283982755667</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.12082138754715</v>
+        <v>7.084291433844984</v>
       </c>
       <c r="C6" t="n">
-        <v>98.69706020334036</v>
+        <v>68.10580173900973</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>25.80131141531043</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>68.15096213340507</v>
+        <v>31.38058361854505</v>
       </c>
       <c r="D7" t="n">
-        <v>35.51275970571987</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>39.22082078466007</v>
+        <v>23.28214680621311</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>28.70630287217673</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.62343515439249</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>33.9468721174462</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>35.89465956267188</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.490029886821772</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.19908996259765</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.490029886821772</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
